--- a/raffle_data.xlsx
+++ b/raffle_data.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duke/Desktop/Claude/TPay/Loyalty web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9609B34E-79B6-A14B-8D6A-2AD35AE063E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C588DD95-2925-904C-BEF3-B21CD793F72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="41120" windowHeight="24100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2380" yWindow="600" windowWidth="36140" windowHeight="23620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Сугалааны жагсаалт" sheetId="1" r:id="rId1"/>
     <sheet name="Зааварчилгаа" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сугалааны жагсаалт'!$A$1:$B$140</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сугалааны жагсаалт'!$A$1:$B$210</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,12 +37,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Бүртгэлтэй утасны дугаар</t>
   </si>
   <si>
     <t>Сугалааны эрх</t>
+  </si>
+  <si>
+    <t>90344618</t>
   </si>
   <si>
     <t>ХЭРХЭН ШИНЭЧЛЭХ ВЭ?</t>
@@ -80,13 +83,13 @@
       <sz val="14"/>
       <color rgb="FF0A1F6E"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -94,7 +97,7 @@
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1593,284 +1596,564 @@
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A141" s="4"/>
-      <c r="B141" s="4"/>
+      <c r="A141" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B141" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A142" s="4"/>
-      <c r="B142" s="4"/>
+      <c r="A142" s="4">
+        <v>86686165</v>
+      </c>
+      <c r="B142" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A143" s="4"/>
-      <c r="B143" s="4"/>
+      <c r="A143" s="4">
+        <v>99725282</v>
+      </c>
+      <c r="B143" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A144" s="4"/>
-      <c r="B144" s="4"/>
+      <c r="A144" s="4">
+        <v>90082848</v>
+      </c>
+      <c r="B144" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A145" s="4"/>
-      <c r="B145" s="4"/>
+      <c r="A145" s="4">
+        <v>96828898</v>
+      </c>
+      <c r="B145" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A146" s="4"/>
-      <c r="B146" s="4"/>
+      <c r="A146" s="4">
+        <v>90545421</v>
+      </c>
+      <c r="B146" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A147" s="4"/>
-      <c r="B147" s="4"/>
+      <c r="A147" s="4">
+        <v>89938981</v>
+      </c>
+      <c r="B147" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A148" s="4"/>
-      <c r="B148" s="4"/>
+      <c r="A148" s="4">
+        <v>95008691</v>
+      </c>
+      <c r="B148" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A149" s="4"/>
-      <c r="B149" s="4"/>
+      <c r="A149" s="4">
+        <v>80646722</v>
+      </c>
+      <c r="B149" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A150" s="4"/>
-      <c r="B150" s="4"/>
+      <c r="A150" s="4">
+        <v>86797917</v>
+      </c>
+      <c r="B150" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A151" s="4"/>
-      <c r="B151" s="4"/>
+      <c r="A151" s="4">
+        <v>99247369</v>
+      </c>
+      <c r="B151" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A152" s="4"/>
-      <c r="B152" s="4"/>
+      <c r="A152" s="4">
+        <v>99510431</v>
+      </c>
+      <c r="B152" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A153" s="4"/>
-      <c r="B153" s="4"/>
+      <c r="A153" s="4">
+        <v>86839676</v>
+      </c>
+      <c r="B153" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A154" s="4"/>
-      <c r="B154" s="4"/>
+      <c r="A154" s="4">
+        <v>80140212</v>
+      </c>
+      <c r="B154" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A155" s="4"/>
-      <c r="B155" s="4"/>
+      <c r="A155" s="4">
+        <v>85557498</v>
+      </c>
+      <c r="B155" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A156" s="4"/>
-      <c r="B156" s="4"/>
+      <c r="A156" s="4">
+        <v>98002068</v>
+      </c>
+      <c r="B156" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A157" s="4"/>
-      <c r="B157" s="4"/>
+      <c r="A157" s="4">
+        <v>86262602</v>
+      </c>
+      <c r="B157" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A158" s="4"/>
-      <c r="B158" s="4"/>
+      <c r="A158" s="4">
+        <v>88484200</v>
+      </c>
+      <c r="B158" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A159" s="4"/>
-      <c r="B159" s="4"/>
+      <c r="A159" s="4">
+        <v>80098101</v>
+      </c>
+      <c r="B159" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A160" s="4"/>
-      <c r="B160" s="4"/>
+      <c r="A160" s="4">
+        <v>90739816</v>
+      </c>
+      <c r="B160" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A161" s="4"/>
-      <c r="B161" s="4"/>
+      <c r="A161" s="4">
+        <v>80184840</v>
+      </c>
+      <c r="B161" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A162" s="4"/>
-      <c r="B162" s="4"/>
+      <c r="A162" s="4">
+        <v>99054580</v>
+      </c>
+      <c r="B162" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A163" s="4"/>
-      <c r="B163" s="4"/>
+      <c r="A163" s="4">
+        <v>85255310</v>
+      </c>
+      <c r="B163" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A164" s="4"/>
-      <c r="B164" s="4"/>
+      <c r="A164" s="4">
+        <v>96505820</v>
+      </c>
+      <c r="B164" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A165" s="4"/>
-      <c r="B165" s="4"/>
+      <c r="A165" s="4">
+        <v>89249288</v>
+      </c>
+      <c r="B165" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A166" s="4"/>
-      <c r="B166" s="4"/>
+      <c r="A166" s="4">
+        <v>90769816</v>
+      </c>
+      <c r="B166" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A167" s="4"/>
-      <c r="B167" s="4"/>
+      <c r="A167" s="4">
+        <v>96620141</v>
+      </c>
+      <c r="B167" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A168" s="4"/>
-      <c r="B168" s="4"/>
+      <c r="A168" s="4">
+        <v>90133434</v>
+      </c>
+      <c r="B168" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A169" s="4"/>
-      <c r="B169" s="4"/>
+      <c r="A169" s="4">
+        <v>95650412</v>
+      </c>
+      <c r="B169" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A170" s="4"/>
-      <c r="B170" s="4"/>
+      <c r="A170" s="4">
+        <v>95544781</v>
+      </c>
+      <c r="B170" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A171" s="4"/>
-      <c r="B171" s="4"/>
+      <c r="A171" s="4">
+        <v>88075352</v>
+      </c>
+      <c r="B171" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A172" s="4"/>
-      <c r="B172" s="4"/>
+      <c r="A172" s="4">
+        <v>86024722</v>
+      </c>
+      <c r="B172" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A173" s="4"/>
-      <c r="B173" s="4"/>
+      <c r="A173" s="4">
+        <v>80927289</v>
+      </c>
+      <c r="B173" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A174" s="4"/>
-      <c r="B174" s="4"/>
+      <c r="A174" s="4">
+        <v>99854976</v>
+      </c>
+      <c r="B174" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A175" s="4"/>
-      <c r="B175" s="4"/>
+      <c r="A175" s="4">
+        <v>96234423</v>
+      </c>
+      <c r="B175" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A176" s="4"/>
-      <c r="B176" s="4"/>
+      <c r="A176" s="4">
+        <v>89360623</v>
+      </c>
+      <c r="B176" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A177" s="4"/>
-      <c r="B177" s="4"/>
+      <c r="A177" s="4">
+        <v>80204225</v>
+      </c>
+      <c r="B177" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A178" s="4"/>
-      <c r="B178" s="4"/>
+      <c r="A178" s="4">
+        <v>95871699</v>
+      </c>
+      <c r="B178" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A179" s="4"/>
-      <c r="B179" s="4"/>
+      <c r="A179" s="4">
+        <v>99961494</v>
+      </c>
+      <c r="B179" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A180" s="4"/>
-      <c r="B180" s="4"/>
+      <c r="A180" s="4">
+        <v>80881366</v>
+      </c>
+      <c r="B180" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A181" s="4"/>
-      <c r="B181" s="4"/>
+      <c r="A181" s="4">
+        <v>94247990</v>
+      </c>
+      <c r="B181" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A182" s="4"/>
-      <c r="B182" s="4"/>
+      <c r="A182" s="4">
+        <v>88853213</v>
+      </c>
+      <c r="B182" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A183" s="4"/>
-      <c r="B183" s="4"/>
+      <c r="A183" s="4">
+        <v>99441382</v>
+      </c>
+      <c r="B183" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A184" s="4"/>
-      <c r="B184" s="4"/>
+      <c r="A184" s="4">
+        <v>91540414</v>
+      </c>
+      <c r="B184" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A185" s="4"/>
-      <c r="B185" s="4"/>
+      <c r="A185" s="4">
+        <v>88394252</v>
+      </c>
+      <c r="B185" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A186" s="4"/>
-      <c r="B186" s="4"/>
+      <c r="A186" s="4">
+        <v>99374426</v>
+      </c>
+      <c r="B186" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A187" s="4"/>
-      <c r="B187" s="4"/>
+      <c r="A187" s="4">
+        <v>90491229</v>
+      </c>
+      <c r="B187" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A188" s="4"/>
-      <c r="B188" s="4"/>
+      <c r="A188" s="4">
+        <v>80387191</v>
+      </c>
+      <c r="B188" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A189" s="4"/>
-      <c r="B189" s="4"/>
+      <c r="A189" s="4">
+        <v>99923426</v>
+      </c>
+      <c r="B189" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A190" s="4"/>
-      <c r="B190" s="4"/>
+      <c r="A190" s="4">
+        <v>88828050</v>
+      </c>
+      <c r="B190" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A191" s="4"/>
-      <c r="B191" s="4"/>
+      <c r="A191" s="4">
+        <v>99227672</v>
+      </c>
+      <c r="B191" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A192" s="4"/>
-      <c r="B192" s="4"/>
+      <c r="A192" s="4">
+        <v>94616191</v>
+      </c>
+      <c r="B192" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A193" s="4"/>
-      <c r="B193" s="4"/>
+      <c r="A193" s="4">
+        <v>99200785</v>
+      </c>
+      <c r="B193" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A194" s="4"/>
-      <c r="B194" s="4"/>
+      <c r="A194" s="4">
+        <v>85112043</v>
+      </c>
+      <c r="B194" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A195" s="4"/>
-      <c r="B195" s="4"/>
+      <c r="A195" s="4">
+        <v>88031542</v>
+      </c>
+      <c r="B195" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A196" s="4"/>
-      <c r="B196" s="4"/>
+      <c r="A196" s="4">
+        <v>98895999</v>
+      </c>
+      <c r="B196" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A197" s="4"/>
-      <c r="B197" s="4"/>
+      <c r="A197" s="4">
+        <v>99395682</v>
+      </c>
+      <c r="B197" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A198" s="4"/>
-      <c r="B198" s="4"/>
+      <c r="A198" s="4">
+        <v>80196752</v>
+      </c>
+      <c r="B198" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A199" s="4"/>
-      <c r="B199" s="4"/>
+      <c r="A199" s="4">
+        <v>95834808</v>
+      </c>
+      <c r="B199" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A200" s="4"/>
-      <c r="B200" s="4"/>
+      <c r="A200" s="4">
+        <v>86690639</v>
+      </c>
+      <c r="B200" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A201" s="4"/>
-      <c r="B201" s="4"/>
+      <c r="A201" s="4">
+        <v>89108108</v>
+      </c>
+      <c r="B201" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A202" s="4"/>
-      <c r="B202" s="4"/>
+      <c r="A202" s="4">
+        <v>90343673</v>
+      </c>
+      <c r="B202" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A203" s="4"/>
-      <c r="B203" s="4"/>
+      <c r="A203" s="4">
+        <v>94745342</v>
+      </c>
+      <c r="B203" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A204" s="4"/>
-      <c r="B204" s="4"/>
+      <c r="A204" s="4">
+        <v>94114285</v>
+      </c>
+      <c r="B204" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A205" s="4"/>
-      <c r="B205" s="4"/>
+      <c r="A205" s="4">
+        <v>88402253</v>
+      </c>
+      <c r="B205" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A206" s="4"/>
-      <c r="B206" s="4"/>
+      <c r="A206" s="4">
+        <v>80631458</v>
+      </c>
+      <c r="B206" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A207" s="4"/>
-      <c r="B207" s="4"/>
+      <c r="A207" s="4">
+        <v>85247876</v>
+      </c>
+      <c r="B207" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A208" s="4"/>
-      <c r="B208" s="4"/>
+      <c r="A208" s="4">
+        <v>86255151</v>
+      </c>
+      <c r="B208" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A209" s="4"/>
-      <c r="B209" s="4"/>
+      <c r="A209" s="4">
+        <v>91113481</v>
+      </c>
+      <c r="B209" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A210" s="4"/>
-      <c r="B210" s="4"/>
+      <c r="A210" s="4">
+        <v>91197656</v>
+      </c>
+      <c r="B210" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A211" s="4"/>
@@ -1969,11 +2252,14 @@
       <c r="B234" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B140" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:B210" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError sqref="A141" numberStoredAsText="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -1987,32 +2273,32 @@
   <sheetData>
     <row r="1" spans="1:1" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/raffle_data.xlsx
+++ b/raffle_data.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/duke/Desktop/Claude/TPay/Loyalty web/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C588DD95-2925-904C-BEF3-B21CD793F72A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DDF20A1-BF07-9E44-93D3-6296324E9F91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2380" yWindow="600" windowWidth="36140" windowHeight="23620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="25600" windowHeight="27060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Сугалааны жагсаалт" sheetId="1" r:id="rId1"/>
     <sheet name="Зааварчилгаа" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сугалааны жагсаалт'!$A$1:$B$210</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Сугалааны жагсаалт'!$A$1:$B$612</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="778">
   <si>
     <t>Бүртгэлтэй утасны дугаар</t>
   </si>
@@ -45,9 +45,6 @@
     <t>Сугалааны эрх</t>
   </si>
   <si>
-    <t>90344618</t>
-  </si>
-  <si>
     <t>ХЭРХЭН ШИНЭЧЛЭХ ВЭ?</t>
   </si>
   <si>
@@ -64,6 +61,2316 @@
   </si>
   <si>
     <t>4. data.json шинэчлэгдэнэ — сайт шууд ажиллана</t>
+  </si>
+  <si>
+    <t>96449901</t>
+  </si>
+  <si>
+    <t>95692659</t>
+  </si>
+  <si>
+    <t>90420717</t>
+  </si>
+  <si>
+    <t>95952808</t>
+  </si>
+  <si>
+    <t>95129017</t>
+  </si>
+  <si>
+    <t>90941504</t>
+  </si>
+  <si>
+    <t>99145910</t>
+  </si>
+  <si>
+    <t>88147497</t>
+  </si>
+  <si>
+    <t>94666576</t>
+  </si>
+  <si>
+    <t>99983428</t>
+  </si>
+  <si>
+    <t>86708555</t>
+  </si>
+  <si>
+    <t>88998640</t>
+  </si>
+  <si>
+    <t>96012310</t>
+  </si>
+  <si>
+    <t>94164810</t>
+  </si>
+  <si>
+    <t>99431142</t>
+  </si>
+  <si>
+    <t>88237541</t>
+  </si>
+  <si>
+    <t>94182528</t>
+  </si>
+  <si>
+    <t>95782267</t>
+  </si>
+  <si>
+    <t>85113609</t>
+  </si>
+  <si>
+    <t>86600220</t>
+  </si>
+  <si>
+    <t>90878678</t>
+  </si>
+  <si>
+    <t>91150087</t>
+  </si>
+  <si>
+    <t>91110565</t>
+  </si>
+  <si>
+    <t>99508140</t>
+  </si>
+  <si>
+    <t>88747029</t>
+  </si>
+  <si>
+    <t>95552610</t>
+  </si>
+  <si>
+    <t>83006787</t>
+  </si>
+  <si>
+    <t>91313230</t>
+  </si>
+  <si>
+    <t>99855572</t>
+  </si>
+  <si>
+    <t>88787740</t>
+  </si>
+  <si>
+    <t>91506969</t>
+  </si>
+  <si>
+    <t>88027033</t>
+  </si>
+  <si>
+    <t>94720572</t>
+  </si>
+  <si>
+    <t>90451331</t>
+  </si>
+  <si>
+    <t>91050411</t>
+  </si>
+  <si>
+    <t>80124240</t>
+  </si>
+  <si>
+    <t>86121026</t>
+  </si>
+  <si>
+    <t>95099526</t>
+  </si>
+  <si>
+    <t>90351297</t>
+  </si>
+  <si>
+    <t>99609484</t>
+  </si>
+  <si>
+    <t>86158004</t>
+  </si>
+  <si>
+    <t>86809330</t>
+  </si>
+  <si>
+    <t>94224400</t>
+  </si>
+  <si>
+    <t>89827981</t>
+  </si>
+  <si>
+    <t>89799966</t>
+  </si>
+  <si>
+    <t>99429496</t>
+  </si>
+  <si>
+    <t>99265958</t>
+  </si>
+  <si>
+    <t>99959245</t>
+  </si>
+  <si>
+    <t>99959238</t>
+  </si>
+  <si>
+    <t>86906577</t>
+  </si>
+  <si>
+    <t>94252593</t>
+  </si>
+  <si>
+    <t>99417921</t>
+  </si>
+  <si>
+    <t>89761256</t>
+  </si>
+  <si>
+    <t>85953131</t>
+  </si>
+  <si>
+    <t>88148803</t>
+  </si>
+  <si>
+    <t>89536484</t>
+  </si>
+  <si>
+    <t>99484793</t>
+  </si>
+  <si>
+    <t>99352569</t>
+  </si>
+  <si>
+    <t>96063125</t>
+  </si>
+  <si>
+    <t>89765875</t>
+  </si>
+  <si>
+    <t>80995774</t>
+  </si>
+  <si>
+    <t>88654160</t>
+  </si>
+  <si>
+    <t>94275854</t>
+  </si>
+  <si>
+    <t>99305914</t>
+  </si>
+  <si>
+    <t>89965876</t>
+  </si>
+  <si>
+    <t>88763261</t>
+  </si>
+  <si>
+    <t>95429927</t>
+  </si>
+  <si>
+    <t>85007399</t>
+  </si>
+  <si>
+    <t>91029994</t>
+  </si>
+  <si>
+    <t>99832479</t>
+  </si>
+  <si>
+    <t>88354142</t>
+  </si>
+  <si>
+    <t>91817970</t>
+  </si>
+  <si>
+    <t>99750005</t>
+  </si>
+  <si>
+    <t>85501412</t>
+  </si>
+  <si>
+    <t>88579544</t>
+  </si>
+  <si>
+    <t>94496832</t>
+  </si>
+  <si>
+    <t>96788586</t>
+  </si>
+  <si>
+    <t>80263386</t>
+  </si>
+  <si>
+    <t>90939397</t>
+  </si>
+  <si>
+    <t>99741948</t>
+  </si>
+  <si>
+    <t>96055056</t>
+  </si>
+  <si>
+    <t>95651701</t>
+  </si>
+  <si>
+    <t>86224289</t>
+  </si>
+  <si>
+    <t>95633696</t>
+  </si>
+  <si>
+    <t>99373071</t>
+  </si>
+  <si>
+    <t>95414030</t>
+  </si>
+  <si>
+    <t>88750157</t>
+  </si>
+  <si>
+    <t>89838757</t>
+  </si>
+  <si>
+    <t>99228231</t>
+  </si>
+  <si>
+    <t>94443094</t>
+  </si>
+  <si>
+    <t>88266107</t>
+  </si>
+  <si>
+    <t>98990606</t>
+  </si>
+  <si>
+    <t>96967633</t>
+  </si>
+  <si>
+    <t>89890075</t>
+  </si>
+  <si>
+    <t>80640704</t>
+  </si>
+  <si>
+    <t>86180999</t>
+  </si>
+  <si>
+    <t>89501801</t>
+  </si>
+  <si>
+    <t>80217128</t>
+  </si>
+  <si>
+    <t>89384096</t>
+  </si>
+  <si>
+    <t>88668883</t>
+  </si>
+  <si>
+    <t>89798940</t>
+  </si>
+  <si>
+    <t>88299944</t>
+  </si>
+  <si>
+    <t>90209908</t>
+  </si>
+  <si>
+    <t>99812054</t>
+  </si>
+  <si>
+    <t>80534445</t>
+  </si>
+  <si>
+    <t>88961566</t>
+  </si>
+  <si>
+    <t>99878476</t>
+  </si>
+  <si>
+    <t>88131970</t>
+  </si>
+  <si>
+    <t>91172538</t>
+  </si>
+  <si>
+    <t>95510093</t>
+  </si>
+  <si>
+    <t>88752293</t>
+  </si>
+  <si>
+    <t>94354584</t>
+  </si>
+  <si>
+    <t>91915282</t>
+  </si>
+  <si>
+    <t>88668893</t>
+  </si>
+  <si>
+    <t>96052805</t>
+  </si>
+  <si>
+    <t>90545421</t>
+  </si>
+  <si>
+    <t>89938981</t>
+  </si>
+  <si>
+    <t>95008691</t>
+  </si>
+  <si>
+    <t>80646722</t>
+  </si>
+  <si>
+    <t>86797917</t>
+  </si>
+  <si>
+    <t>99247369</t>
+  </si>
+  <si>
+    <t>99510431</t>
+  </si>
+  <si>
+    <t>94129676</t>
+  </si>
+  <si>
+    <t>80140212</t>
+  </si>
+  <si>
+    <t>85557498</t>
+  </si>
+  <si>
+    <t>86262602</t>
+  </si>
+  <si>
+    <t>88484200</t>
+  </si>
+  <si>
+    <t>80098101</t>
+  </si>
+  <si>
+    <t>90739816</t>
+  </si>
+  <si>
+    <t>80184840</t>
+  </si>
+  <si>
+    <t>99054580</t>
+  </si>
+  <si>
+    <t>85255310</t>
+  </si>
+  <si>
+    <t>96505820</t>
+  </si>
+  <si>
+    <t>89249288</t>
+  </si>
+  <si>
+    <t>90769816</t>
+  </si>
+  <si>
+    <t>96620141</t>
+  </si>
+  <si>
+    <t>90133434</t>
+  </si>
+  <si>
+    <t>95650412</t>
+  </si>
+  <si>
+    <t>95544781</t>
+  </si>
+  <si>
+    <t>86024722</t>
+  </si>
+  <si>
+    <t>96234423</t>
+  </si>
+  <si>
+    <t>89360623</t>
+  </si>
+  <si>
+    <t>95871699</t>
+  </si>
+  <si>
+    <t>99961494</t>
+  </si>
+  <si>
+    <t>80881366</t>
+  </si>
+  <si>
+    <t>94247990</t>
+  </si>
+  <si>
+    <t>88853213</t>
+  </si>
+  <si>
+    <t>99441382</t>
+  </si>
+  <si>
+    <t>91540414</t>
+  </si>
+  <si>
+    <t>88394252</t>
+  </si>
+  <si>
+    <t>99374426</t>
+  </si>
+  <si>
+    <t>99923426</t>
+  </si>
+  <si>
+    <t>88828050</t>
+  </si>
+  <si>
+    <t>94616191</t>
+  </si>
+  <si>
+    <t>99200785</t>
+  </si>
+  <si>
+    <t>85112043</t>
+  </si>
+  <si>
+    <t>88031542</t>
+  </si>
+  <si>
+    <t>98895999</t>
+  </si>
+  <si>
+    <t>99395682</t>
+  </si>
+  <si>
+    <t>80196752</t>
+  </si>
+  <si>
+    <t>86690639</t>
+  </si>
+  <si>
+    <t>90343673</t>
+  </si>
+  <si>
+    <t>94745342</t>
+  </si>
+  <si>
+    <t>94114285</t>
+  </si>
+  <si>
+    <t>88402253</t>
+  </si>
+  <si>
+    <t>80631458</t>
+  </si>
+  <si>
+    <t>85247876</t>
+  </si>
+  <si>
+    <t>86255151</t>
+  </si>
+  <si>
+    <t>91113481</t>
+  </si>
+  <si>
+    <t>91197656</t>
+  </si>
+  <si>
+    <t>91876373</t>
+  </si>
+  <si>
+    <t>85345922</t>
+  </si>
+  <si>
+    <t>88827813</t>
+  </si>
+  <si>
+    <t>80748208</t>
+  </si>
+  <si>
+    <t>99528156</t>
+  </si>
+  <si>
+    <t>95615257</t>
+  </si>
+  <si>
+    <t>80596966</t>
+  </si>
+  <si>
+    <t>96228001</t>
+  </si>
+  <si>
+    <t>86563040</t>
+  </si>
+  <si>
+    <t>94936767</t>
+  </si>
+  <si>
+    <t>88258156</t>
+  </si>
+  <si>
+    <t>88583944</t>
+  </si>
+  <si>
+    <t>80126373</t>
+  </si>
+  <si>
+    <t>86110126</t>
+  </si>
+  <si>
+    <t>99938774</t>
+  </si>
+  <si>
+    <t>96796069</t>
+  </si>
+  <si>
+    <t>80338689</t>
+  </si>
+  <si>
+    <t>99558383</t>
+  </si>
+  <si>
+    <t>89896199</t>
+  </si>
+  <si>
+    <t>88186435</t>
+  </si>
+  <si>
+    <t>98853131</t>
+  </si>
+  <si>
+    <t>86110119</t>
+  </si>
+  <si>
+    <t>88691545</t>
+  </si>
+  <si>
+    <t>86918289</t>
+  </si>
+  <si>
+    <t>95499571</t>
+  </si>
+  <si>
+    <t>95470505</t>
+  </si>
+  <si>
+    <t>99368428</t>
+  </si>
+  <si>
+    <t>99951378</t>
+  </si>
+  <si>
+    <t>80411008</t>
+  </si>
+  <si>
+    <t>88668884</t>
+  </si>
+  <si>
+    <t>95527559</t>
+  </si>
+  <si>
+    <t>89910928</t>
+  </si>
+  <si>
+    <t>99785914</t>
+  </si>
+  <si>
+    <t>80310342</t>
+  </si>
+  <si>
+    <t>89873109</t>
+  </si>
+  <si>
+    <t>86682223</t>
+  </si>
+  <si>
+    <t>97000304</t>
+  </si>
+  <si>
+    <t>99321528</t>
+  </si>
+  <si>
+    <t>88819217</t>
+  </si>
+  <si>
+    <t>80836546</t>
+  </si>
+  <si>
+    <t>80661805</t>
+  </si>
+  <si>
+    <t>80607677</t>
+  </si>
+  <si>
+    <t>91910538</t>
+  </si>
+  <si>
+    <t>91817005</t>
+  </si>
+  <si>
+    <t>86004118</t>
+  </si>
+  <si>
+    <t>96970578</t>
+  </si>
+  <si>
+    <t>99853568</t>
+  </si>
+  <si>
+    <t>85861565</t>
+  </si>
+  <si>
+    <t>88964094</t>
+  </si>
+  <si>
+    <t>99821703</t>
+  </si>
+  <si>
+    <t>80011226</t>
+  </si>
+  <si>
+    <t>94062028</t>
+  </si>
+  <si>
+    <t>88313232</t>
+  </si>
+  <si>
+    <t>90064606</t>
+  </si>
+  <si>
+    <t>95224999</t>
+  </si>
+  <si>
+    <t>99903528</t>
+  </si>
+  <si>
+    <t>95327909</t>
+  </si>
+  <si>
+    <t>89999829</t>
+  </si>
+  <si>
+    <t>94388834</t>
+  </si>
+  <si>
+    <t>94440577</t>
+  </si>
+  <si>
+    <t>90010713</t>
+  </si>
+  <si>
+    <t>99712999</t>
+  </si>
+  <si>
+    <t>80877626</t>
+  </si>
+  <si>
+    <t>85690826</t>
+  </si>
+  <si>
+    <t>95075878</t>
+  </si>
+  <si>
+    <t>99938216</t>
+  </si>
+  <si>
+    <t>88591151</t>
+  </si>
+  <si>
+    <t>95364208</t>
+  </si>
+  <si>
+    <t>91189111</t>
+  </si>
+  <si>
+    <t>85812496</t>
+  </si>
+  <si>
+    <t>89961710</t>
+  </si>
+  <si>
+    <t>80832506</t>
+  </si>
+  <si>
+    <t>89555441</t>
+  </si>
+  <si>
+    <t>99960666</t>
+  </si>
+  <si>
+    <t>89845066</t>
+  </si>
+  <si>
+    <t>86930410</t>
+  </si>
+  <si>
+    <t>83115554</t>
+  </si>
+  <si>
+    <t>90800518</t>
+  </si>
+  <si>
+    <t>99010458</t>
+  </si>
+  <si>
+    <t>86027711</t>
+  </si>
+  <si>
+    <t>94228229</t>
+  </si>
+  <si>
+    <t>88603494</t>
+  </si>
+  <si>
+    <t>95503290</t>
+  </si>
+  <si>
+    <t>99356188</t>
+  </si>
+  <si>
+    <t>96033777</t>
+  </si>
+  <si>
+    <t>85857672</t>
+  </si>
+  <si>
+    <t>89585905</t>
+  </si>
+  <si>
+    <t>89890733</t>
+  </si>
+  <si>
+    <t>96201114</t>
+  </si>
+  <si>
+    <t>88315437</t>
+  </si>
+  <si>
+    <t>99467912</t>
+  </si>
+  <si>
+    <t>86842820</t>
+  </si>
+  <si>
+    <t>88042442</t>
+  </si>
+  <si>
+    <t>85984046</t>
+  </si>
+  <si>
+    <t>89828605</t>
+  </si>
+  <si>
+    <t>85157546</t>
+  </si>
+  <si>
+    <t>99254176</t>
+  </si>
+  <si>
+    <t>94345070</t>
+  </si>
+  <si>
+    <t>99507065</t>
+  </si>
+  <si>
+    <t>99636515</t>
+  </si>
+  <si>
+    <t>85357132</t>
+  </si>
+  <si>
+    <t>99736657</t>
+  </si>
+  <si>
+    <t>86619117</t>
+  </si>
+  <si>
+    <t>85447003</t>
+  </si>
+  <si>
+    <t>86857005</t>
+  </si>
+  <si>
+    <t>89281097</t>
+  </si>
+  <si>
+    <t>99521246</t>
+  </si>
+  <si>
+    <t>99251930</t>
+  </si>
+  <si>
+    <t>90901403</t>
+  </si>
+  <si>
+    <t>85661523</t>
+  </si>
+  <si>
+    <t>85369602</t>
+  </si>
+  <si>
+    <t>90505907</t>
+  </si>
+  <si>
+    <t>95079011</t>
+  </si>
+  <si>
+    <t>86173346</t>
+  </si>
+  <si>
+    <t>97071614</t>
+  </si>
+  <si>
+    <t>94988629</t>
+  </si>
+  <si>
+    <t>94565770</t>
+  </si>
+  <si>
+    <t>88668614</t>
+  </si>
+  <si>
+    <t>80789978</t>
+  </si>
+  <si>
+    <t>85477418</t>
+  </si>
+  <si>
+    <t>88267676</t>
+  </si>
+  <si>
+    <t>91444998</t>
+  </si>
+  <si>
+    <t>88525241</t>
+  </si>
+  <si>
+    <t>80836626</t>
+  </si>
+  <si>
+    <t>89699079</t>
+  </si>
+  <si>
+    <t>86605585</t>
+  </si>
+  <si>
+    <t>85247005</t>
+  </si>
+  <si>
+    <t>94917277</t>
+  </si>
+  <si>
+    <t>91214323</t>
+  </si>
+  <si>
+    <t>95577129</t>
+  </si>
+  <si>
+    <t>99135766</t>
+  </si>
+  <si>
+    <t>99963781</t>
+  </si>
+  <si>
+    <t>99375653</t>
+  </si>
+  <si>
+    <t>99402035</t>
+  </si>
+  <si>
+    <t>89138425</t>
+  </si>
+  <si>
+    <t>85622797</t>
+  </si>
+  <si>
+    <t>80847392</t>
+  </si>
+  <si>
+    <t>90022637</t>
+  </si>
+  <si>
+    <t>88303154</t>
+  </si>
+  <si>
+    <t>90917728</t>
+  </si>
+  <si>
+    <t>89209923</t>
+  </si>
+  <si>
+    <t>88872264</t>
+  </si>
+  <si>
+    <t>89666476</t>
+  </si>
+  <si>
+    <t>80859771</t>
+  </si>
+  <si>
+    <t>90208811</t>
+  </si>
+  <si>
+    <t>99799911</t>
+  </si>
+  <si>
+    <t>89792414</t>
+  </si>
+  <si>
+    <t>86241433</t>
+  </si>
+  <si>
+    <t>80601462</t>
+  </si>
+  <si>
+    <t>99415020</t>
+  </si>
+  <si>
+    <t>97110977</t>
+  </si>
+  <si>
+    <t>88845074</t>
+  </si>
+  <si>
+    <t>85544318</t>
+  </si>
+  <si>
+    <t>91779299</t>
+  </si>
+  <si>
+    <t>95671091</t>
+  </si>
+  <si>
+    <t>96612031</t>
+  </si>
+  <si>
+    <t>88949870</t>
+  </si>
+  <si>
+    <t>86265299</t>
+  </si>
+  <si>
+    <t>86569181</t>
+  </si>
+  <si>
+    <t>95800822</t>
+  </si>
+  <si>
+    <t>91530408</t>
+  </si>
+  <si>
+    <t>94906299</t>
+  </si>
+  <si>
+    <t>86854128</t>
+  </si>
+  <si>
+    <t>80787307</t>
+  </si>
+  <si>
+    <t>88058937</t>
+  </si>
+  <si>
+    <t>94914696</t>
+  </si>
+  <si>
+    <t>85375750</t>
+  </si>
+  <si>
+    <t>94505452</t>
+  </si>
+  <si>
+    <t>89206200</t>
+  </si>
+  <si>
+    <t>86211719</t>
+  </si>
+  <si>
+    <t>80964243</t>
+  </si>
+  <si>
+    <t>94649363</t>
+  </si>
+  <si>
+    <t>94532093</t>
+  </si>
+  <si>
+    <t>80701703</t>
+  </si>
+  <si>
+    <t>86261998</t>
+  </si>
+  <si>
+    <t>89148910</t>
+  </si>
+  <si>
+    <t>94124404</t>
+  </si>
+  <si>
+    <t>96690819</t>
+  </si>
+  <si>
+    <t>98173427</t>
+  </si>
+  <si>
+    <t>95342499</t>
+  </si>
+  <si>
+    <t>86686165</t>
+  </si>
+  <si>
+    <t>99725282</t>
+  </si>
+  <si>
+    <t>90212041</t>
+  </si>
+  <si>
+    <t>99041037</t>
+  </si>
+  <si>
+    <t>86160997</t>
+  </si>
+  <si>
+    <t>88874536</t>
+  </si>
+  <si>
+    <t>91526555</t>
+  </si>
+  <si>
+    <t>96705600</t>
+  </si>
+  <si>
+    <t>99556522</t>
+  </si>
+  <si>
+    <t>95645428</t>
+  </si>
+  <si>
+    <t>89978671</t>
+  </si>
+  <si>
+    <t>88742595</t>
+  </si>
+  <si>
+    <t>85230113</t>
+  </si>
+  <si>
+    <t>94288752</t>
+  </si>
+  <si>
+    <t>80114176</t>
+  </si>
+  <si>
+    <t>85474878</t>
+  </si>
+  <si>
+    <t>99782843</t>
+  </si>
+  <si>
+    <t>96447677</t>
+  </si>
+  <si>
+    <t>88753706</t>
+  </si>
+  <si>
+    <t>99508606</t>
+  </si>
+  <si>
+    <t>90809821</t>
+  </si>
+  <si>
+    <t>91369119</t>
+  </si>
+  <si>
+    <t>88243082</t>
+  </si>
+  <si>
+    <t>95782040</t>
+  </si>
+  <si>
+    <t>99305780</t>
+  </si>
+  <si>
+    <t>88759510</t>
+  </si>
+  <si>
+    <t>89724646</t>
+  </si>
+  <si>
+    <t>85181002</t>
+  </si>
+  <si>
+    <t>80979085</t>
+  </si>
+  <si>
+    <t>95674647</t>
+  </si>
+  <si>
+    <t>96974696</t>
+  </si>
+  <si>
+    <t>99646658</t>
+  </si>
+  <si>
+    <t>99263088</t>
+  </si>
+  <si>
+    <t>60056646</t>
+  </si>
+  <si>
+    <t>80403165</t>
+  </si>
+  <si>
+    <t>95639936</t>
+  </si>
+  <si>
+    <t>91157309</t>
+  </si>
+  <si>
+    <t>85207090</t>
+  </si>
+  <si>
+    <t>90592455</t>
+  </si>
+  <si>
+    <t>88253149</t>
+  </si>
+  <si>
+    <t>86828398</t>
+  </si>
+  <si>
+    <t>90710059</t>
+  </si>
+  <si>
+    <t>94424158</t>
+  </si>
+  <si>
+    <t>94148595</t>
+  </si>
+  <si>
+    <t>85016737</t>
+  </si>
+  <si>
+    <t>95955403</t>
+  </si>
+  <si>
+    <t>85299192</t>
+  </si>
+  <si>
+    <t>99647922</t>
+  </si>
+  <si>
+    <t>80408488</t>
+  </si>
+  <si>
+    <t>99368731</t>
+  </si>
+  <si>
+    <t>69912060</t>
+  </si>
+  <si>
+    <t>95913270</t>
+  </si>
+  <si>
+    <t>94961862</t>
+  </si>
+  <si>
+    <t>96064008</t>
+  </si>
+  <si>
+    <t>80170618</t>
+  </si>
+  <si>
+    <t>88324789</t>
+  </si>
+  <si>
+    <t>99574992</t>
+  </si>
+  <si>
+    <t>89655588</t>
+  </si>
+  <si>
+    <t>88664994</t>
+  </si>
+  <si>
+    <t>95863818</t>
+  </si>
+  <si>
+    <t>85149664</t>
+  </si>
+  <si>
+    <t>89275357</t>
+  </si>
+  <si>
+    <t>90113876</t>
+  </si>
+  <si>
+    <t>80909854</t>
+  </si>
+  <si>
+    <t>85240058</t>
+  </si>
+  <si>
+    <t>80197588</t>
+  </si>
+  <si>
+    <t>86044445</t>
+  </si>
+  <si>
+    <t>80220586</t>
+  </si>
+  <si>
+    <t>89902727</t>
+  </si>
+  <si>
+    <t>89068920</t>
+  </si>
+  <si>
+    <t>88246030</t>
+  </si>
+  <si>
+    <t>95032054</t>
+  </si>
+  <si>
+    <t>88062471</t>
+  </si>
+  <si>
+    <t>85299947</t>
+  </si>
+  <si>
+    <t>99442339</t>
+  </si>
+  <si>
+    <t>99625432</t>
+  </si>
+  <si>
+    <t>99571240</t>
+  </si>
+  <si>
+    <t>99273004</t>
+  </si>
+  <si>
+    <t>88127570</t>
+  </si>
+  <si>
+    <t>86188196</t>
+  </si>
+  <si>
+    <t>88908036</t>
+  </si>
+  <si>
+    <t>99502247</t>
+  </si>
+  <si>
+    <t>88950495</t>
+  </si>
+  <si>
+    <t>90112833</t>
+  </si>
+  <si>
+    <t>99234088</t>
+  </si>
+  <si>
+    <t>88699606</t>
+  </si>
+  <si>
+    <t>94400899</t>
+  </si>
+  <si>
+    <t>85500415</t>
+  </si>
+  <si>
+    <t>86947973</t>
+  </si>
+  <si>
+    <t>96018458</t>
+  </si>
+  <si>
+    <t>99283522</t>
+  </si>
+  <si>
+    <t>90151549</t>
+  </si>
+  <si>
+    <t>80496401</t>
+  </si>
+  <si>
+    <t>85455797</t>
+  </si>
+  <si>
+    <t>86070245</t>
+  </si>
+  <si>
+    <t>80130062</t>
+  </si>
+  <si>
+    <t>98084898</t>
+  </si>
+  <si>
+    <t>66187181</t>
+  </si>
+  <si>
+    <t>85118279</t>
+  </si>
+  <si>
+    <t>94706761</t>
+  </si>
+  <si>
+    <t>89842112</t>
+  </si>
+  <si>
+    <t>91558832</t>
+  </si>
+  <si>
+    <t>86225461</t>
+  </si>
+  <si>
+    <t>86506414</t>
+  </si>
+  <si>
+    <t>80677279</t>
+  </si>
+  <si>
+    <t>88988069</t>
+  </si>
+  <si>
+    <t>85390962</t>
+  </si>
+  <si>
+    <t>80437305</t>
+  </si>
+  <si>
+    <t>99134408</t>
+  </si>
+  <si>
+    <t>89960624</t>
+  </si>
+  <si>
+    <t>99593228</t>
+  </si>
+  <si>
+    <t>99480195</t>
+  </si>
+  <si>
+    <t>89571808</t>
+  </si>
+  <si>
+    <t>91690802</t>
+  </si>
+  <si>
+    <t>88940466</t>
+  </si>
+  <si>
+    <t>89116739</t>
+  </si>
+  <si>
+    <t>89787369</t>
+  </si>
+  <si>
+    <t>89780960</t>
+  </si>
+  <si>
+    <t>88203200</t>
+  </si>
+  <si>
+    <t>80245476</t>
+  </si>
+  <si>
+    <t>88131963</t>
+  </si>
+  <si>
+    <t>91011137</t>
+  </si>
+  <si>
+    <t>80132244</t>
+  </si>
+  <si>
+    <t>80778936</t>
+  </si>
+  <si>
+    <t>89723840</t>
+  </si>
+  <si>
+    <t>86635666</t>
+  </si>
+  <si>
+    <t>91555135</t>
+  </si>
+  <si>
+    <t>83110707</t>
+  </si>
+  <si>
+    <t>99806795</t>
+  </si>
+  <si>
+    <t>86537401</t>
+  </si>
+  <si>
+    <t>88754041</t>
+  </si>
+  <si>
+    <t>99957373</t>
+  </si>
+  <si>
+    <t>91699614</t>
+  </si>
+  <si>
+    <t>55140335</t>
+  </si>
+  <si>
+    <t>89993050</t>
+  </si>
+  <si>
+    <t>60605371</t>
+  </si>
+  <si>
+    <t>91260095</t>
+  </si>
+  <si>
+    <t>90649995</t>
+  </si>
+  <si>
+    <t>95702760</t>
+  </si>
+  <si>
+    <t>85138313</t>
+  </si>
+  <si>
+    <t>95342112</t>
+  </si>
+  <si>
+    <t>89183068</t>
+  </si>
+  <si>
+    <t>96180618</t>
+  </si>
+  <si>
+    <t>99493359</t>
+  </si>
+  <si>
+    <t>89397779</t>
+  </si>
+  <si>
+    <t>99630755</t>
+  </si>
+  <si>
+    <t>99905073</t>
+  </si>
+  <si>
+    <t>88959121</t>
+  </si>
+  <si>
+    <t>89963283</t>
+  </si>
+  <si>
+    <t>88201496</t>
+  </si>
+  <si>
+    <t>88739071</t>
+  </si>
+  <si>
+    <t>91921090</t>
+  </si>
+  <si>
+    <t>85831246</t>
+  </si>
+  <si>
+    <t>95959870</t>
+  </si>
+  <si>
+    <t>80390905</t>
+  </si>
+  <si>
+    <t>95390389</t>
+  </si>
+  <si>
+    <t>80162598</t>
+  </si>
+  <si>
+    <t>88443838</t>
+  </si>
+  <si>
+    <t>89922764</t>
+  </si>
+  <si>
+    <t>89471170</t>
+  </si>
+  <si>
+    <t>88424206</t>
+  </si>
+  <si>
+    <t>94280563</t>
+  </si>
+  <si>
+    <t>94500155</t>
+  </si>
+  <si>
+    <t>95242297</t>
+  </si>
+  <si>
+    <t>88640035</t>
+  </si>
+  <si>
+    <t>99515840</t>
+  </si>
+  <si>
+    <t>80447588</t>
+  </si>
+  <si>
+    <t>85629900</t>
+  </si>
+  <si>
+    <t>99131577</t>
+  </si>
+  <si>
+    <t>94971552</t>
+  </si>
+  <si>
+    <t>99610604</t>
+  </si>
+  <si>
+    <t>85300969</t>
+  </si>
+  <si>
+    <t>88848979</t>
+  </si>
+  <si>
+    <t>99601369</t>
+  </si>
+  <si>
+    <t>91776962</t>
+  </si>
+  <si>
+    <t>91161799</t>
+  </si>
+  <si>
+    <t>99341393</t>
+  </si>
+  <si>
+    <t>88903977</t>
+  </si>
+  <si>
+    <t>85003932</t>
+  </si>
+  <si>
+    <t>91870322</t>
+  </si>
+  <si>
+    <t>80821566</t>
+  </si>
+  <si>
+    <t>94121751</t>
+  </si>
+  <si>
+    <t>80990856</t>
+  </si>
+  <si>
+    <t>96760712</t>
+  </si>
+  <si>
+    <t>99140870</t>
+  </si>
+  <si>
+    <t>95973603</t>
+  </si>
+  <si>
+    <t>96696133</t>
+  </si>
+  <si>
+    <t>88206765</t>
+  </si>
+  <si>
+    <t>89215262</t>
+  </si>
+  <si>
+    <t>83023355</t>
+  </si>
+  <si>
+    <t>89146169</t>
+  </si>
+  <si>
+    <t>95042044</t>
+  </si>
+  <si>
+    <t>90143999</t>
+  </si>
+  <si>
+    <t>89582127</t>
+  </si>
+  <si>
+    <t>95181494</t>
+  </si>
+  <si>
+    <t>99439804</t>
+  </si>
+  <si>
+    <t>88378795</t>
+  </si>
+  <si>
+    <t>88972505</t>
+  </si>
+  <si>
+    <t>99737494</t>
+  </si>
+  <si>
+    <t>94840258</t>
+  </si>
+  <si>
+    <t>88959751</t>
+  </si>
+  <si>
+    <t>95364874</t>
+  </si>
+  <si>
+    <t>89951803</t>
+  </si>
+  <si>
+    <t>99318681</t>
+  </si>
+  <si>
+    <t>80121094</t>
+  </si>
+  <si>
+    <t>99748136</t>
+  </si>
+  <si>
+    <t>99638473</t>
+  </si>
+  <si>
+    <t>91240090</t>
+  </si>
+  <si>
+    <t>99518495</t>
+  </si>
+  <si>
+    <t>86654494</t>
+  </si>
+  <si>
+    <t>94549612</t>
+  </si>
+  <si>
+    <t>90116904</t>
+  </si>
+  <si>
+    <t>80401420</t>
+  </si>
+  <si>
+    <t>94444100</t>
+  </si>
+  <si>
+    <t>88936931</t>
+  </si>
+  <si>
+    <t>88208894</t>
+  </si>
+  <si>
+    <t>95939108</t>
+  </si>
+  <si>
+    <t>99892893</t>
+  </si>
+  <si>
+    <t>86131783</t>
+  </si>
+  <si>
+    <t>96353040</t>
+  </si>
+  <si>
+    <t>96688683</t>
+  </si>
+  <si>
+    <t>88701257</t>
+  </si>
+  <si>
+    <t>94422740</t>
+  </si>
+  <si>
+    <t>80850924</t>
+  </si>
+  <si>
+    <t>86310334</t>
+  </si>
+  <si>
+    <t>89181831</t>
+  </si>
+  <si>
+    <t>86216969</t>
+  </si>
+  <si>
+    <t>99034220</t>
+  </si>
+  <si>
+    <t>94837083</t>
+  </si>
+  <si>
+    <t>94420446</t>
+  </si>
+  <si>
+    <t>60666754</t>
+  </si>
+  <si>
+    <t>99245520</t>
+  </si>
+  <si>
+    <t>80496100</t>
+  </si>
+  <si>
+    <t>90113425</t>
+  </si>
+  <si>
+    <t>89626507</t>
+  </si>
+  <si>
+    <t>99687916</t>
+  </si>
+  <si>
+    <t>88728789</t>
+  </si>
+  <si>
+    <t>99289232</t>
+  </si>
+  <si>
+    <t>99265650</t>
+  </si>
+  <si>
+    <t>88257730</t>
+  </si>
+  <si>
+    <t>95955962</t>
+  </si>
+  <si>
+    <t>99778560</t>
+  </si>
+  <si>
+    <t>86757320</t>
+  </si>
+  <si>
+    <t>85860807</t>
+  </si>
+  <si>
+    <t>80006142</t>
+  </si>
+  <si>
+    <t>88424293</t>
+  </si>
+  <si>
+    <t>86909545</t>
+  </si>
+  <si>
+    <t>88812001</t>
+  </si>
+  <si>
+    <t>80114871</t>
+  </si>
+  <si>
+    <t>94189562</t>
+  </si>
+  <si>
+    <t>90970313</t>
+  </si>
+  <si>
+    <t>89197191</t>
+  </si>
+  <si>
+    <t>88164778</t>
+  </si>
+  <si>
+    <t>95741626</t>
+  </si>
+  <si>
+    <t>85600153</t>
+  </si>
+  <si>
+    <t>95917631</t>
+  </si>
+  <si>
+    <t>95114380</t>
+  </si>
+  <si>
+    <t>96870306</t>
+  </si>
+  <si>
+    <t>95026768</t>
+  </si>
+  <si>
+    <t>80436892</t>
+  </si>
+  <si>
+    <t>88950683</t>
+  </si>
+  <si>
+    <t>94629121</t>
+  </si>
+  <si>
+    <t>99693883</t>
+  </si>
+  <si>
+    <t>86699494</t>
+  </si>
+  <si>
+    <t>80283940</t>
+  </si>
+  <si>
+    <t>95399916</t>
+  </si>
+  <si>
+    <t>80170767</t>
+  </si>
+  <si>
+    <t>99688847</t>
+  </si>
+  <si>
+    <t>86248428</t>
+  </si>
+  <si>
+    <t>91600053</t>
+  </si>
+  <si>
+    <t>99024714</t>
+  </si>
+  <si>
+    <t>85117019</t>
+  </si>
+  <si>
+    <t>80673733</t>
+  </si>
+  <si>
+    <t>86834699</t>
+  </si>
+  <si>
+    <t>69601108</t>
+  </si>
+  <si>
+    <t>89801228</t>
+  </si>
+  <si>
+    <t>88328778</t>
+  </si>
+  <si>
+    <t>86528680</t>
+  </si>
+  <si>
+    <t>88044835</t>
+  </si>
+  <si>
+    <t>99559094</t>
+  </si>
+  <si>
+    <t>60082517</t>
+  </si>
+  <si>
+    <t>98987590</t>
+  </si>
+  <si>
+    <t>85960426</t>
+  </si>
+  <si>
+    <t>91171236</t>
+  </si>
+  <si>
+    <t>99498513</t>
+  </si>
+  <si>
+    <t>99531145</t>
+  </si>
+  <si>
+    <t>94740879</t>
+  </si>
+  <si>
+    <t>99570007</t>
+  </si>
+  <si>
+    <t>86901056</t>
+  </si>
+  <si>
+    <t>99650048</t>
+  </si>
+  <si>
+    <t>80720836</t>
+  </si>
+  <si>
+    <t>80146336</t>
+  </si>
+  <si>
+    <t>88707502</t>
+  </si>
+  <si>
+    <t>99269391</t>
+  </si>
+  <si>
+    <t>88157465</t>
+  </si>
+  <si>
+    <t>91997986</t>
+  </si>
+  <si>
+    <t>90166110</t>
+  </si>
+  <si>
+    <t>96280415</t>
+  </si>
+  <si>
+    <t>91203084</t>
+  </si>
+  <si>
+    <t>89390455</t>
+  </si>
+  <si>
+    <t>66121997</t>
+  </si>
+  <si>
+    <t>85261940</t>
+  </si>
+  <si>
+    <t>88961644</t>
+  </si>
+  <si>
+    <t>95173565</t>
+  </si>
+  <si>
+    <t>88684459</t>
+  </si>
+  <si>
+    <t>99498959</t>
+  </si>
+  <si>
+    <t>95501213</t>
+  </si>
+  <si>
+    <t>80051026</t>
+  </si>
+  <si>
+    <t>95973278</t>
+  </si>
+  <si>
+    <t>86921341</t>
+  </si>
+  <si>
+    <t>80881813</t>
+  </si>
+  <si>
+    <t>88532208</t>
+  </si>
+  <si>
+    <t>99574006</t>
+  </si>
+  <si>
+    <t>88120915</t>
+  </si>
+  <si>
+    <t>88352464</t>
+  </si>
+  <si>
+    <t>99344089</t>
+  </si>
+  <si>
+    <t>99398911</t>
+  </si>
+  <si>
+    <t>86215979</t>
+  </si>
+  <si>
+    <t>99862071</t>
+  </si>
+  <si>
+    <t>99665275</t>
+  </si>
+  <si>
+    <t>85521867</t>
+  </si>
+  <si>
+    <t>91160217</t>
+  </si>
+  <si>
+    <t>96474994</t>
+  </si>
+  <si>
+    <t>90483048</t>
+  </si>
+  <si>
+    <t>89589981</t>
+  </si>
+  <si>
+    <t>99922871</t>
+  </si>
+  <si>
+    <t>88255639</t>
+  </si>
+  <si>
+    <t>85868694</t>
+  </si>
+  <si>
+    <t>94530549</t>
+  </si>
+  <si>
+    <t>99716422</t>
+  </si>
+  <si>
+    <t>85644607</t>
+  </si>
+  <si>
+    <t>66375463</t>
+  </si>
+  <si>
+    <t>88675097</t>
+  </si>
+  <si>
+    <t>80893806</t>
+  </si>
+  <si>
+    <t>95120831</t>
+  </si>
+  <si>
+    <t>94667993</t>
+  </si>
+  <si>
+    <t>86981986</t>
+  </si>
+  <si>
+    <t>91430717</t>
+  </si>
+  <si>
+    <t>85880588</t>
+  </si>
+  <si>
+    <t>85234070</t>
+  </si>
+  <si>
+    <t>88226217</t>
+  </si>
+  <si>
+    <t>88701059</t>
+  </si>
+  <si>
+    <t>89078837</t>
+  </si>
+  <si>
+    <t>88399302</t>
+  </si>
+  <si>
+    <t>99043139</t>
+  </si>
+  <si>
+    <t>80307999</t>
+  </si>
+  <si>
+    <t>88508952</t>
+  </si>
+  <si>
+    <t>94461738</t>
+  </si>
+  <si>
+    <t>86151530</t>
+  </si>
+  <si>
+    <t>89119024</t>
+  </si>
+  <si>
+    <t>95244661</t>
+  </si>
+  <si>
+    <t>88122769</t>
+  </si>
+  <si>
+    <t>88652500</t>
+  </si>
+  <si>
+    <t>94843945</t>
+  </si>
+  <si>
+    <t>95080836</t>
+  </si>
+  <si>
+    <t>80325265</t>
+  </si>
+  <si>
+    <t>99483338</t>
+  </si>
+  <si>
+    <t>94261029</t>
+  </si>
+  <si>
+    <t>80449303</t>
+  </si>
+  <si>
+    <t>99415210</t>
+  </si>
+  <si>
+    <t>99798441</t>
+  </si>
+  <si>
+    <t>80002352</t>
+  </si>
+  <si>
+    <t>88862498</t>
+  </si>
+  <si>
+    <t>96611938</t>
+  </si>
+  <si>
+    <t>95828154</t>
+  </si>
+  <si>
+    <t>90336603</t>
+  </si>
+  <si>
+    <t>89847489</t>
+  </si>
+  <si>
+    <t>89775454</t>
+  </si>
+  <si>
+    <t>88890713</t>
+  </si>
+  <si>
+    <t>85448619</t>
+  </si>
+  <si>
+    <t>99269612</t>
+  </si>
+  <si>
+    <t>94725282</t>
+  </si>
+  <si>
+    <t>95808939</t>
+  </si>
+  <si>
+    <t>98003781</t>
+  </si>
+  <si>
+    <t>99483116</t>
+  </si>
+  <si>
+    <t>80816679</t>
+  </si>
+  <si>
+    <t>99464190</t>
+  </si>
+  <si>
+    <t>99740054</t>
+  </si>
+  <si>
+    <t>95959103</t>
+  </si>
+  <si>
+    <t>96886638</t>
+  </si>
+  <si>
+    <t>89990695</t>
+  </si>
+  <si>
+    <t>90112704</t>
+  </si>
+  <si>
+    <t>88363406</t>
+  </si>
+  <si>
+    <t>90509666</t>
+  </si>
+  <si>
+    <t>88218729</t>
+  </si>
+  <si>
+    <t>94494591</t>
+  </si>
+  <si>
+    <t>95039791</t>
+  </si>
+  <si>
+    <t>94183562</t>
+  </si>
+  <si>
+    <t>85403886</t>
+  </si>
+  <si>
+    <t>96381978</t>
+  </si>
+  <si>
+    <t>98002068</t>
+  </si>
+  <si>
+    <t>88075352</t>
+  </si>
+  <si>
+    <t>80927289</t>
+  </si>
+  <si>
+    <t>99854976</t>
+  </si>
+  <si>
+    <t>80204225</t>
+  </si>
+  <si>
+    <t>80387191</t>
+  </si>
+  <si>
+    <t>99227672</t>
+  </si>
+  <si>
+    <t>91800305</t>
+  </si>
+  <si>
+    <t>98082606</t>
+  </si>
+  <si>
+    <t>99987540</t>
+  </si>
+  <si>
+    <t>99872111</t>
+  </si>
+  <si>
+    <t>85841403</t>
+  </si>
+  <si>
+    <t>90313887</t>
+  </si>
+  <si>
+    <t>86830322</t>
+  </si>
+  <si>
+    <t>89942380</t>
+  </si>
+  <si>
+    <t>90190279</t>
+  </si>
+  <si>
+    <t>88515200</t>
+  </si>
+  <si>
+    <t>80227228</t>
+  </si>
+  <si>
+    <t>86307676</t>
+  </si>
+  <si>
+    <t>80485856</t>
+  </si>
+  <si>
+    <t>80008209</t>
+  </si>
+  <si>
+    <t>80146484</t>
+  </si>
+  <si>
+    <t>86881818</t>
+  </si>
+  <si>
+    <t>80091023</t>
+  </si>
+  <si>
+    <t>94445079</t>
+  </si>
+  <si>
+    <t>99508927</t>
+  </si>
+  <si>
+    <t>95959875</t>
+  </si>
+  <si>
+    <t>95854762</t>
+  </si>
+  <si>
+    <t>89558983</t>
+  </si>
+  <si>
+    <t>95939800</t>
   </si>
 </sst>
 </file>
@@ -83,13 +2390,13 @@
       <sz val="14"/>
       <color rgb="FF0A1F6E"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -97,7 +2404,7 @@
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -121,7 +2428,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -144,11 +2451,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -158,11 +2480,45 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFC0FFC0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -468,7 +2824,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B234"/>
+  <dimension ref="A1:C771"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -484,1782 +2840,6212 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
-        <v>85403886</v>
+      <c r="A2" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="B2" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
-        <v>95039791</v>
+      <c r="A3" s="6" t="s">
+        <v>9</v>
       </c>
       <c r="B3" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
-        <v>90112704</v>
+      <c r="A4" s="6" t="s">
+        <v>10</v>
       </c>
       <c r="B4" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
-        <v>89890733</v>
+      <c r="A5" s="6" t="s">
+        <v>11</v>
       </c>
       <c r="B5" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
-        <v>99464190</v>
+      <c r="A6" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="B6" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
-        <v>91189111</v>
+      <c r="A7" s="6" t="s">
+        <v>13</v>
       </c>
       <c r="B7" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
-        <v>85357132</v>
+      <c r="A8" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="B8" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
-        <v>99736657</v>
+      <c r="A9" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="B9" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="4">
-        <v>94345070</v>
+      <c r="A10" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="B10" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="4">
-        <v>96808210</v>
+      <c r="A11" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="B11" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="4">
-        <v>85857672</v>
+      <c r="A12" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="B12" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="4">
-        <v>95503290</v>
+      <c r="A13" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="B13" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="4">
-        <v>94228229</v>
+      <c r="A14" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="B14" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="4">
-        <v>90374546</v>
+      <c r="A15" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="B15" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="4">
-        <v>95914606</v>
+      <c r="A16" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="B16" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="4">
-        <v>86027711</v>
+      <c r="A17" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="B17" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="4">
-        <v>89281097</v>
+      <c r="A18" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="B18" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A19" s="4">
-        <v>86857005</v>
+      <c r="A19" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="B19" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A20" s="4">
-        <v>86930410</v>
+      <c r="A20" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="B20" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A21" s="4">
-        <v>80848975</v>
+      <c r="A21" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="B21" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A22" s="4">
-        <v>99251930</v>
+      <c r="A22" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="B22" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A23" s="4">
-        <v>88603494</v>
+      <c r="A23" s="6" t="s">
+        <v>29</v>
       </c>
       <c r="B23" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A24" s="4">
-        <v>80832506</v>
+      <c r="A24" s="6" t="s">
+        <v>30</v>
       </c>
       <c r="B24" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="4">
-        <v>86842820</v>
+      <c r="A25" s="6" t="s">
+        <v>31</v>
       </c>
       <c r="B25" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="4">
-        <v>99960666</v>
+      <c r="A26" s="6" t="s">
+        <v>32</v>
       </c>
       <c r="B26" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" s="4">
-        <v>89961710</v>
+      <c r="A27" s="6" t="s">
+        <v>33</v>
       </c>
       <c r="B27" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" s="4">
-        <v>85812496</v>
+      <c r="A28" s="6" t="s">
+        <v>34</v>
       </c>
       <c r="B28" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A29" s="4">
-        <v>90505907</v>
+      <c r="A29" s="6" t="s">
+        <v>35</v>
       </c>
       <c r="B29" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A30" s="4">
-        <v>89845066</v>
+      <c r="A30" s="6" t="s">
+        <v>36</v>
       </c>
       <c r="B30" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A31" s="4">
-        <v>88315437</v>
+      <c r="A31" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="B31" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A32" s="4">
-        <v>96886638</v>
+      <c r="A32" s="6" t="s">
+        <v>38</v>
       </c>
       <c r="B32" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A33" s="4">
-        <v>89585905</v>
+      <c r="A33" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="B33" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A34" s="4">
-        <v>80789978</v>
+      <c r="A34" s="6" t="s">
+        <v>40</v>
       </c>
       <c r="B34" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A35" s="4">
-        <v>97071614</v>
+      <c r="A35" s="6" t="s">
+        <v>41</v>
       </c>
       <c r="B35" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A36" s="4">
-        <v>99636515</v>
+      <c r="A36" s="6" t="s">
+        <v>42</v>
       </c>
       <c r="B36" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A37" s="4">
-        <v>99483116</v>
+      <c r="A37" s="6" t="s">
+        <v>43</v>
       </c>
       <c r="B37" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A38" s="4">
-        <v>94988629</v>
+      <c r="A38" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="B38" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A39" s="4">
-        <v>94183562</v>
+      <c r="A39" s="6" t="s">
+        <v>45</v>
       </c>
       <c r="B39" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A40" s="4">
-        <v>85661523</v>
+      <c r="A40" s="6" t="s">
+        <v>46</v>
       </c>
       <c r="B40" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A41" s="4">
-        <v>88218729</v>
+      <c r="A41" s="6" t="s">
+        <v>47</v>
       </c>
       <c r="B41" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A42" s="4">
-        <v>95959103</v>
+      <c r="A42" s="6" t="s">
+        <v>48</v>
       </c>
       <c r="B42" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A43" s="4">
-        <v>83040666</v>
+      <c r="A43" s="6" t="s">
+        <v>49</v>
       </c>
       <c r="B43" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A44" s="4">
-        <v>85477418</v>
+      <c r="A44" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="B44" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A45" s="4">
-        <v>88363406</v>
+      <c r="A45" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="B45" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A46" s="4">
-        <v>88668614</v>
+      <c r="A46" s="6" t="s">
+        <v>52</v>
       </c>
       <c r="B46" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A47" s="4">
-        <v>85369602</v>
+      <c r="A47" s="6" t="s">
+        <v>53</v>
       </c>
       <c r="B47" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A48" s="4">
-        <v>96033777</v>
+      <c r="A48" s="6" t="s">
+        <v>54</v>
       </c>
       <c r="B48" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A49" s="4">
-        <v>99010458</v>
+      <c r="A49" s="6" t="s">
+        <v>55</v>
       </c>
       <c r="B49" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A50" s="4">
-        <v>88042442</v>
+      <c r="A50" s="6" t="s">
+        <v>56</v>
       </c>
       <c r="B50" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A51" s="4">
-        <v>89990695</v>
+      <c r="A51" s="6" t="s">
+        <v>57</v>
       </c>
       <c r="B51" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A52" s="4">
-        <v>90800518</v>
+      <c r="A52" s="6" t="s">
+        <v>58</v>
       </c>
       <c r="B52" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A53" s="4">
-        <v>96201114</v>
+      <c r="A53" s="6" t="s">
+        <v>59</v>
       </c>
       <c r="B53" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A54" s="4">
-        <v>90901403</v>
+      <c r="A54" s="6" t="s">
+        <v>60</v>
       </c>
       <c r="B54" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A55" s="4">
-        <v>99254176</v>
+      <c r="A55" s="6" t="s">
+        <v>61</v>
       </c>
       <c r="B55" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A56" s="4">
-        <v>99467912</v>
+      <c r="A56" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="B56" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A57" s="4">
-        <v>89555441</v>
+      <c r="A57" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="B57" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A58" s="4">
-        <v>99521246</v>
+      <c r="A58" s="6" t="s">
+        <v>64</v>
       </c>
       <c r="B58" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A59" s="4">
-        <v>86619117</v>
+      <c r="A59" s="6" t="s">
+        <v>65</v>
       </c>
       <c r="B59" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A60" s="4">
-        <v>89828605</v>
+      <c r="A60" s="6" t="s">
+        <v>66</v>
       </c>
       <c r="B60" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A61" s="4">
-        <v>85984046</v>
+      <c r="A61" s="6" t="s">
+        <v>67</v>
       </c>
       <c r="B61" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A62" s="4">
-        <v>95079011</v>
+      <c r="A62" s="6" t="s">
+        <v>68</v>
       </c>
       <c r="B62" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A63" s="4">
-        <v>98003781</v>
+      <c r="A63" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="B63" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A64" s="4">
-        <v>94565770</v>
+      <c r="A64" s="6" t="s">
+        <v>70</v>
       </c>
       <c r="B64" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A65" s="4">
-        <v>90509666</v>
+      <c r="A65" s="6" t="s">
+        <v>71</v>
       </c>
       <c r="B65" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A66" s="4">
-        <v>99740054</v>
+      <c r="A66" s="6" t="s">
+        <v>72</v>
       </c>
       <c r="B66" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A67" s="4">
-        <v>86173346</v>
+      <c r="A67" s="6" t="s">
+        <v>73</v>
       </c>
       <c r="B67" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A68" s="4">
-        <v>85447003</v>
+      <c r="A68" s="6" t="s">
+        <v>74</v>
       </c>
       <c r="B68" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A69" s="4">
-        <v>99705623</v>
+      <c r="A69" s="6" t="s">
+        <v>75</v>
       </c>
       <c r="B69" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A70" s="4">
-        <v>85157546</v>
+      <c r="A70" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="B70" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A71" s="4">
-        <v>86160136</v>
+      <c r="A71" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="B71" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A72" s="4">
-        <v>99507065</v>
+      <c r="A72" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="B72" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A73" s="4">
-        <v>94494591</v>
+      <c r="A73" s="6" t="s">
+        <v>79</v>
       </c>
       <c r="B73" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A74" s="4">
-        <v>99356188</v>
+      <c r="A74" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="B74" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A75" s="4">
-        <v>80816679</v>
+      <c r="A75" s="6" t="s">
+        <v>81</v>
       </c>
       <c r="B75" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A76" s="4">
-        <v>95808939</v>
+      <c r="A76" s="6" t="s">
+        <v>82</v>
       </c>
       <c r="B76" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A77" s="4">
-        <v>88267676</v>
+      <c r="A77" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="B77" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A78" s="4">
-        <v>91444998</v>
+      <c r="A78" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="B78" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A79" s="4">
-        <v>88525241</v>
+      <c r="A79" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="B79" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A80" s="4">
-        <v>80836626</v>
+      <c r="A80" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="B80" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A81" s="4">
-        <v>89699079</v>
+      <c r="A81" s="6" t="s">
+        <v>87</v>
       </c>
       <c r="B81" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A82" s="4">
-        <v>86605585</v>
+      <c r="A82" s="6" t="s">
+        <v>88</v>
       </c>
       <c r="B82" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A83" s="4">
-        <v>96381978</v>
+      <c r="A83" s="6" t="s">
+        <v>89</v>
       </c>
       <c r="B83" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A84" s="4">
-        <v>85247005</v>
+      <c r="A84" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="B84" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A85" s="4">
-        <v>94917277</v>
+      <c r="A85" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="B85" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A86" s="4">
-        <v>91214323</v>
+      <c r="A86" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="B86" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A87" s="4">
-        <v>95577129</v>
+      <c r="A87" s="6" t="s">
+        <v>93</v>
       </c>
       <c r="B87" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A88" s="4">
-        <v>99135766</v>
+      <c r="A88" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="B88" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A89" s="4">
-        <v>99963781</v>
+      <c r="A89" s="6" t="s">
+        <v>95</v>
       </c>
       <c r="B89" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A90" s="4">
-        <v>99375653</v>
+      <c r="A90" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="B90" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A91" s="4">
-        <v>99402035</v>
+      <c r="A91" s="6" t="s">
+        <v>97</v>
       </c>
       <c r="B91" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A92" s="4">
-        <v>89138425</v>
+      <c r="A92" s="6" t="s">
+        <v>98</v>
       </c>
       <c r="B92" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A93" s="4">
-        <v>85622797</v>
+      <c r="A93" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="B93" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A94" s="4">
-        <v>80847392</v>
+      <c r="A94" s="6" t="s">
+        <v>100</v>
       </c>
       <c r="B94" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A95" s="4">
-        <v>90022637</v>
+      <c r="A95" s="6" t="s">
+        <v>101</v>
       </c>
       <c r="B95" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A96" s="4">
-        <v>88303154</v>
+      <c r="A96" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="B96" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A97" s="4">
-        <v>90917728</v>
+      <c r="A97" s="6" t="s">
+        <v>103</v>
       </c>
       <c r="B97" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A98" s="4">
-        <v>89209923</v>
+      <c r="A98" s="6" t="s">
+        <v>104</v>
       </c>
       <c r="B98" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A99" s="4">
-        <v>88872264</v>
+      <c r="A99" s="6" t="s">
+        <v>105</v>
       </c>
       <c r="B99" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A100" s="4">
-        <v>89666476</v>
+      <c r="A100" s="6" t="s">
+        <v>106</v>
       </c>
       <c r="B100" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A101" s="4">
-        <v>80859771</v>
+      <c r="A101" s="6" t="s">
+        <v>107</v>
       </c>
       <c r="B101" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A102" s="4">
-        <v>90208811</v>
+      <c r="A102" s="6" t="s">
+        <v>108</v>
       </c>
       <c r="B102" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A103" s="4">
-        <v>99799911</v>
+      <c r="A103" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="B103" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A104" s="4">
-        <v>89792414</v>
+      <c r="A104" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="B104" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A105" s="4">
-        <v>86241433</v>
+      <c r="A105" s="6" t="s">
+        <v>111</v>
       </c>
       <c r="B105" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A106" s="4">
-        <v>88144510</v>
+      <c r="A106" s="6" t="s">
+        <v>112</v>
       </c>
       <c r="B106" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A107" s="4">
-        <v>80601462</v>
+      <c r="A107" s="6" t="s">
+        <v>113</v>
       </c>
       <c r="B107" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A108" s="4">
-        <v>99415020</v>
+      <c r="A108" s="6" t="s">
+        <v>114</v>
       </c>
       <c r="B108" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A109" s="4">
-        <v>97110977</v>
+      <c r="A109" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="B109" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A110" s="4">
-        <v>88845074</v>
+      <c r="A110" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="B110" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A111" s="4">
-        <v>85544318</v>
+      <c r="A111" s="6" t="s">
+        <v>117</v>
       </c>
       <c r="B111" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A112" s="4">
-        <v>91779299</v>
+      <c r="A112" s="6" t="s">
+        <v>118</v>
       </c>
       <c r="B112" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A113" s="4">
-        <v>95671091</v>
+      <c r="A113" s="6" t="s">
+        <v>119</v>
       </c>
       <c r="B113" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A114" s="4">
-        <v>96612031</v>
+      <c r="A114" s="6" t="s">
+        <v>120</v>
       </c>
       <c r="B114" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A115" s="4">
-        <v>88949870</v>
+      <c r="A115" s="6" t="s">
+        <v>121</v>
       </c>
       <c r="B115" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A116" s="4">
-        <v>86265299</v>
+      <c r="A116" s="6" t="s">
+        <v>122</v>
       </c>
       <c r="B116" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A117" s="4">
-        <v>86569181</v>
+      <c r="A117" s="6" t="s">
+        <v>123</v>
       </c>
       <c r="B117" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A118" s="4">
-        <v>95800822</v>
+      <c r="A118" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="B118" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A119" s="4">
-        <v>91530408</v>
+      <c r="A119" s="6" t="s">
+        <v>125</v>
       </c>
       <c r="B119" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A120" s="4">
-        <v>94906299</v>
+      <c r="A120" s="6" t="s">
+        <v>126</v>
       </c>
       <c r="B120" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A121" s="4">
-        <v>86854128</v>
+      <c r="A121" s="6" t="s">
+        <v>127</v>
       </c>
       <c r="B121" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A122" s="4">
-        <v>80787307</v>
+      <c r="A122" s="6" t="s">
+        <v>128</v>
       </c>
       <c r="B122" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A123" s="4">
-        <v>88058937</v>
+      <c r="A123" s="6" t="s">
+        <v>129</v>
       </c>
       <c r="B123" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A124" s="4">
-        <v>94914696</v>
+      <c r="A124" s="6" t="s">
+        <v>130</v>
       </c>
       <c r="B124" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A125" s="4">
-        <v>85375750</v>
+      <c r="A125" s="6" t="s">
+        <v>131</v>
       </c>
       <c r="B125" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A126" s="4">
-        <v>94505452</v>
+      <c r="A126" s="6" t="s">
+        <v>132</v>
       </c>
       <c r="B126" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A127" s="4">
-        <v>89206200</v>
+      <c r="A127" s="6" t="s">
+        <v>133</v>
       </c>
       <c r="B127" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A128" s="4">
-        <v>86211719</v>
+      <c r="A128" s="6" t="s">
+        <v>134</v>
       </c>
       <c r="B128" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A129" s="4">
-        <v>80964243</v>
+      <c r="A129" s="6" t="s">
+        <v>135</v>
       </c>
       <c r="B129" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A130" s="4">
-        <v>94649363</v>
+      <c r="A130" s="6" t="s">
+        <v>136</v>
       </c>
       <c r="B130" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A131" s="4">
-        <v>94532093</v>
+      <c r="A131" s="6" t="s">
+        <v>137</v>
       </c>
       <c r="B131" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A132" s="4">
-        <v>80701703</v>
+      <c r="A132" s="6" t="s">
+        <v>138</v>
       </c>
       <c r="B132" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A133" s="4">
-        <v>86261998</v>
+      <c r="A133" s="6" t="s">
+        <v>139</v>
       </c>
       <c r="B133" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A134" s="4">
-        <v>85086989</v>
+      <c r="A134" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="B134" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A135" s="4">
-        <v>89148910</v>
+      <c r="A135" s="6" t="s">
+        <v>141</v>
       </c>
       <c r="B135" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A136" s="4">
-        <v>94124404</v>
+      <c r="A136" s="6" t="s">
+        <v>142</v>
       </c>
       <c r="B136" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A137" s="4">
-        <v>96690819</v>
+      <c r="A137" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="B137" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A138" s="4">
-        <v>98173427</v>
+      <c r="A138" s="6" t="s">
+        <v>144</v>
       </c>
       <c r="B138" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A139" s="4">
-        <v>94202969</v>
+      <c r="A139" s="6" t="s">
+        <v>145</v>
       </c>
       <c r="B139" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A140" s="4">
-        <v>95342499</v>
+      <c r="A140" s="6" t="s">
+        <v>146</v>
       </c>
       <c r="B140" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A141" s="4" t="s">
-        <v>2</v>
+      <c r="A141" s="6" t="s">
+        <v>147</v>
       </c>
       <c r="B141" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A142" s="4">
-        <v>86686165</v>
+      <c r="A142" s="6" t="s">
+        <v>148</v>
       </c>
       <c r="B142" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A143" s="4">
-        <v>99725282</v>
+      <c r="A143" s="6" t="s">
+        <v>149</v>
       </c>
       <c r="B143" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A144" s="4">
-        <v>90082848</v>
+      <c r="A144" s="6" t="s">
+        <v>150</v>
       </c>
       <c r="B144" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A145" s="4">
-        <v>96828898</v>
+      <c r="A145" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="B145" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A146" s="4">
-        <v>90545421</v>
+      <c r="A146" s="6" t="s">
+        <v>152</v>
       </c>
       <c r="B146" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A147" s="4">
-        <v>89938981</v>
+      <c r="A147" s="6" t="s">
+        <v>153</v>
       </c>
       <c r="B147" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A148" s="4">
-        <v>95008691</v>
+      <c r="A148" s="6" t="s">
+        <v>154</v>
       </c>
       <c r="B148" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A149" s="4">
-        <v>80646722</v>
+      <c r="A149" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="B149" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A150" s="4">
-        <v>86797917</v>
+      <c r="A150" s="6" t="s">
+        <v>156</v>
       </c>
       <c r="B150" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A151" s="4">
-        <v>99247369</v>
+      <c r="A151" s="6" t="s">
+        <v>157</v>
       </c>
       <c r="B151" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A152" s="4">
-        <v>99510431</v>
+      <c r="A152" s="6" t="s">
+        <v>158</v>
       </c>
       <c r="B152" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A153" s="4">
-        <v>86839676</v>
+      <c r="A153" s="6" t="s">
+        <v>159</v>
       </c>
       <c r="B153" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A154" s="4">
-        <v>80140212</v>
+      <c r="A154" s="6" t="s">
+        <v>160</v>
       </c>
       <c r="B154" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A155" s="4">
-        <v>85557498</v>
+      <c r="A155" s="6" t="s">
+        <v>161</v>
       </c>
       <c r="B155" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A156" s="4">
-        <v>98002068</v>
+      <c r="A156" s="6" t="s">
+        <v>162</v>
       </c>
       <c r="B156" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A157" s="4">
-        <v>86262602</v>
+      <c r="A157" s="6" t="s">
+        <v>163</v>
       </c>
       <c r="B157" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A158" s="4">
-        <v>88484200</v>
+      <c r="A158" s="6" t="s">
+        <v>164</v>
       </c>
       <c r="B158" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A159" s="4">
-        <v>80098101</v>
+      <c r="A159" s="6" t="s">
+        <v>165</v>
       </c>
       <c r="B159" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A160" s="4">
-        <v>90739816</v>
+      <c r="A160" s="6" t="s">
+        <v>166</v>
       </c>
       <c r="B160" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A161" s="4">
-        <v>80184840</v>
+      <c r="A161" s="6" t="s">
+        <v>167</v>
       </c>
       <c r="B161" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A162" s="4">
-        <v>99054580</v>
+      <c r="A162" s="6" t="s">
+        <v>168</v>
       </c>
       <c r="B162" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A163" s="4">
-        <v>85255310</v>
+      <c r="A163" s="6" t="s">
+        <v>169</v>
       </c>
       <c r="B163" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A164" s="4">
-        <v>96505820</v>
+      <c r="A164" s="6" t="s">
+        <v>170</v>
       </c>
       <c r="B164" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A165" s="4">
-        <v>89249288</v>
+      <c r="A165" s="6" t="s">
+        <v>171</v>
       </c>
       <c r="B165" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A166" s="4">
-        <v>90769816</v>
+      <c r="A166" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="B166" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A167" s="4">
-        <v>96620141</v>
+      <c r="A167" s="6" t="s">
+        <v>173</v>
       </c>
       <c r="B167" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A168" s="4">
-        <v>90133434</v>
+      <c r="A168" s="6" t="s">
+        <v>174</v>
       </c>
       <c r="B168" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A169" s="4">
-        <v>95650412</v>
+      <c r="A169" s="6" t="s">
+        <v>175</v>
       </c>
       <c r="B169" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A170" s="4">
-        <v>95544781</v>
+      <c r="A170" s="6" t="s">
+        <v>176</v>
       </c>
       <c r="B170" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A171" s="4">
-        <v>88075352</v>
+      <c r="A171" s="6" t="s">
+        <v>177</v>
       </c>
       <c r="B171" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A172" s="4">
-        <v>86024722</v>
+      <c r="A172" s="6" t="s">
+        <v>178</v>
       </c>
       <c r="B172" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A173" s="4">
-        <v>80927289</v>
+      <c r="A173" s="6" t="s">
+        <v>179</v>
       </c>
       <c r="B173" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A174" s="4">
-        <v>99854976</v>
+      <c r="A174" s="6" t="s">
+        <v>180</v>
       </c>
       <c r="B174" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A175" s="4">
-        <v>96234423</v>
+      <c r="A175" s="6" t="s">
+        <v>181</v>
       </c>
       <c r="B175" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A176" s="4">
-        <v>89360623</v>
+      <c r="A176" s="6" t="s">
+        <v>182</v>
       </c>
       <c r="B176" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A177" s="4">
-        <v>80204225</v>
+      <c r="A177" s="6" t="s">
+        <v>183</v>
       </c>
       <c r="B177" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A178" s="4">
-        <v>95871699</v>
+      <c r="A178" s="6" t="s">
+        <v>184</v>
       </c>
       <c r="B178" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A179" s="4">
-        <v>99961494</v>
+      <c r="A179" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="B179" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A180" s="4">
-        <v>80881366</v>
+      <c r="A180" s="6" t="s">
+        <v>186</v>
       </c>
       <c r="B180" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A181" s="4">
-        <v>94247990</v>
+      <c r="A181" s="6" t="s">
+        <v>187</v>
       </c>
       <c r="B181" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A182" s="4">
-        <v>88853213</v>
+      <c r="A182" s="6" t="s">
+        <v>188</v>
       </c>
       <c r="B182" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A183" s="4">
-        <v>99441382</v>
+      <c r="A183" s="6" t="s">
+        <v>189</v>
       </c>
       <c r="B183" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A184" s="4">
-        <v>91540414</v>
+      <c r="A184" s="6" t="s">
+        <v>190</v>
       </c>
       <c r="B184" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A185" s="4">
-        <v>88394252</v>
+      <c r="A185" s="6" t="s">
+        <v>191</v>
       </c>
       <c r="B185" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A186" s="4">
-        <v>99374426</v>
+      <c r="A186" s="6" t="s">
+        <v>192</v>
       </c>
       <c r="B186" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A187" s="4">
-        <v>90491229</v>
+      <c r="A187" s="6" t="s">
+        <v>193</v>
       </c>
       <c r="B187" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A188" s="4">
-        <v>80387191</v>
+      <c r="A188" s="6" t="s">
+        <v>194</v>
       </c>
       <c r="B188" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A189" s="4">
-        <v>99923426</v>
+      <c r="A189" s="6" t="s">
+        <v>195</v>
       </c>
       <c r="B189" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A190" s="4">
-        <v>88828050</v>
+      <c r="A190" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="B190" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A191" s="4">
-        <v>99227672</v>
+      <c r="A191" s="6" t="s">
+        <v>197</v>
       </c>
       <c r="B191" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A192" s="4">
-        <v>94616191</v>
+      <c r="A192" s="6" t="s">
+        <v>198</v>
       </c>
       <c r="B192" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A193" s="4">
-        <v>99200785</v>
+      <c r="A193" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="B193" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A194" s="4">
-        <v>85112043</v>
+      <c r="A194" s="6" t="s">
+        <v>200</v>
       </c>
       <c r="B194" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A195" s="4">
-        <v>88031542</v>
+      <c r="A195" s="6" t="s">
+        <v>201</v>
       </c>
       <c r="B195" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A196" s="4">
-        <v>98895999</v>
+      <c r="A196" s="6" t="s">
+        <v>202</v>
       </c>
       <c r="B196" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A197" s="4">
-        <v>99395682</v>
+      <c r="A197" s="6" t="s">
+        <v>203</v>
       </c>
       <c r="B197" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A198" s="4">
-        <v>80196752</v>
+      <c r="A198" s="6" t="s">
+        <v>204</v>
       </c>
       <c r="B198" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A199" s="4">
-        <v>95834808</v>
+      <c r="A199" s="6" t="s">
+        <v>205</v>
       </c>
       <c r="B199" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A200" s="4">
-        <v>86690639</v>
+      <c r="A200" s="6" t="s">
+        <v>206</v>
       </c>
       <c r="B200" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A201" s="4">
-        <v>89108108</v>
+      <c r="A201" s="6" t="s">
+        <v>207</v>
       </c>
       <c r="B201" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A202" s="4">
-        <v>90343673</v>
+      <c r="A202" s="6" t="s">
+        <v>208</v>
       </c>
       <c r="B202" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A203" s="4">
-        <v>94745342</v>
+      <c r="A203" s="6" t="s">
+        <v>209</v>
       </c>
       <c r="B203" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A204" s="4">
-        <v>94114285</v>
+      <c r="A204" s="6" t="s">
+        <v>210</v>
       </c>
       <c r="B204" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A205" s="4">
-        <v>88402253</v>
+      <c r="A205" s="6" t="s">
+        <v>211</v>
       </c>
       <c r="B205" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A206" s="4">
-        <v>80631458</v>
+      <c r="A206" s="6" t="s">
+        <v>212</v>
       </c>
       <c r="B206" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A207" s="4">
-        <v>85247876</v>
+      <c r="A207" s="6" t="s">
+        <v>213</v>
       </c>
       <c r="B207" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A208" s="4">
-        <v>86255151</v>
+      <c r="A208" s="6" t="s">
+        <v>214</v>
       </c>
       <c r="B208" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A209" s="4">
-        <v>91113481</v>
+      <c r="A209" s="6" t="s">
+        <v>215</v>
       </c>
       <c r="B209" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A210" s="4">
-        <v>91197656</v>
+      <c r="A210" s="6" t="s">
+        <v>216</v>
       </c>
       <c r="B210" s="4">
         <v>1</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A211" s="4"/>
-      <c r="B211" s="4"/>
+      <c r="A211" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="B211" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A212" s="4"/>
-      <c r="B212" s="4"/>
+      <c r="A212" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B212" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A213" s="4"/>
-      <c r="B213" s="4"/>
+      <c r="A213" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B213" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A214" s="4"/>
-      <c r="B214" s="4"/>
+      <c r="A214" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B214" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A215" s="4"/>
-      <c r="B215" s="4"/>
+      <c r="A215" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="B215" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A216" s="4"/>
-      <c r="B216" s="4"/>
+      <c r="A216" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B216" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A217" s="4"/>
-      <c r="B217" s="4"/>
+      <c r="A217" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B217" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A218" s="4"/>
-      <c r="B218" s="4"/>
+      <c r="A218" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B218" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A219" s="4"/>
-      <c r="B219" s="4"/>
+      <c r="A219" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="B219" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A220" s="4"/>
-      <c r="B220" s="4"/>
+      <c r="A220" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B220" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A221" s="4"/>
-      <c r="B221" s="4"/>
+      <c r="A221" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B221" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A222" s="4"/>
-      <c r="B222" s="4"/>
+      <c r="A222" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B222" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A223" s="4"/>
-      <c r="B223" s="4"/>
+      <c r="A223" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B223" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A224" s="4"/>
-      <c r="B224" s="4"/>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A225" s="4"/>
-      <c r="B225" s="4"/>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A226" s="4"/>
-      <c r="B226" s="4"/>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A227" s="4"/>
-      <c r="B227" s="4"/>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A228" s="4"/>
-      <c r="B228" s="4"/>
-    </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A229" s="4"/>
-      <c r="B229" s="4"/>
-    </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A230" s="4"/>
-      <c r="B230" s="4"/>
-    </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A231" s="4"/>
-      <c r="B231" s="4"/>
-    </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A232" s="4"/>
-      <c r="B232" s="4"/>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A233" s="4"/>
-      <c r="B233" s="4"/>
-    </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A234" s="4"/>
-      <c r="B234" s="4"/>
+      <c r="A224" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="B224" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A225" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="B225" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A226" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B226" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A227" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="B227" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A228" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="B228" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A229" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="B229" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A230" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="B230" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A231" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B231" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A232" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B232" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A233" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="B233" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A234" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="B234" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A235" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B235" s="4">
+        <v>1</v>
+      </c>
+      <c r="C235" s="5"/>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A236" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B236" s="4">
+        <v>1</v>
+      </c>
+      <c r="C236" s="5"/>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A237" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="B237" s="4">
+        <v>1</v>
+      </c>
+      <c r="C237" s="5"/>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A238" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="B238" s="4">
+        <v>1</v>
+      </c>
+      <c r="C238" s="5"/>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A239" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="B239" s="4">
+        <v>1</v>
+      </c>
+      <c r="C239" s="5"/>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A240" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="B240" s="4">
+        <v>1</v>
+      </c>
+      <c r="C240" s="5"/>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A241" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="B241" s="4">
+        <v>1</v>
+      </c>
+      <c r="C241" s="5"/>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A242" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="B242" s="4">
+        <v>1</v>
+      </c>
+      <c r="C242" s="5"/>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A243" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="B243" s="4">
+        <v>1</v>
+      </c>
+      <c r="C243" s="5"/>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A244" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B244" s="4">
+        <v>1</v>
+      </c>
+      <c r="C244" s="5"/>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A245" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="B245" s="4">
+        <v>1</v>
+      </c>
+      <c r="C245" s="5"/>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A246" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="B246" s="4">
+        <v>1</v>
+      </c>
+      <c r="C246" s="5"/>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A247" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="B247" s="4">
+        <v>1</v>
+      </c>
+      <c r="C247" s="5"/>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A248" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B248" s="4">
+        <v>1</v>
+      </c>
+      <c r="C248" s="5"/>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A249" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="B249" s="4">
+        <v>1</v>
+      </c>
+      <c r="C249" s="5"/>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A250" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="B250" s="4">
+        <v>1</v>
+      </c>
+      <c r="C250" s="5"/>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A251" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B251" s="4">
+        <v>1</v>
+      </c>
+      <c r="C251" s="5"/>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A252" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B252" s="4">
+        <v>1</v>
+      </c>
+      <c r="C252" s="5"/>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A253" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="B253" s="4">
+        <v>1</v>
+      </c>
+      <c r="C253" s="5"/>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A254" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="B254" s="4">
+        <v>1</v>
+      </c>
+      <c r="C254" s="5"/>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A255" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="B255" s="4">
+        <v>1</v>
+      </c>
+      <c r="C255" s="5"/>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A256" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B256" s="4">
+        <v>1</v>
+      </c>
+      <c r="C256" s="5"/>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A257" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="B257" s="4">
+        <v>1</v>
+      </c>
+      <c r="C257" s="5"/>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A258" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="B258" s="4">
+        <v>1</v>
+      </c>
+      <c r="C258" s="5"/>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A259" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B259" s="4">
+        <v>1</v>
+      </c>
+      <c r="C259" s="5"/>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A260" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="B260" s="4">
+        <v>1</v>
+      </c>
+      <c r="C260" s="5"/>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A261" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B261" s="4">
+        <v>1</v>
+      </c>
+      <c r="C261" s="5"/>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A262" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="B262" s="4">
+        <v>1</v>
+      </c>
+      <c r="C262" s="5"/>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A263" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="B263" s="4">
+        <v>1</v>
+      </c>
+      <c r="C263" s="5"/>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A264" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B264" s="4">
+        <v>1</v>
+      </c>
+      <c r="C264" s="5"/>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A265" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="B265" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A266" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B266" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A267" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B267" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A268" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B268" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A269" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="B269" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A270" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="B270" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A271" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="B271" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A272" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B272" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A273" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B273" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A274" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="B274" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A275" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="B275" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A276" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="B276" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A277" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="B277" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A278" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="B278" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A279" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="B279" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A280" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B280" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A281" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="B281" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A282" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="B282" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A283" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="B283" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A284" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="B284" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A285" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="B285" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A286" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="B286" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A287" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="B287" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A288" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="B288" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A289" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="B289" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A290" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="B290" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A291" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="B291" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A292" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="B292" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A293" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="B293" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A294" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="B294" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A295" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="B295" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A296" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="B296" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A297" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="B297" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A298" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="B298" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A299" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="B299" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A300" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="B300" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A301" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="B301" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A302" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="B302" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A303" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="B303" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A304" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="B304" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A305" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="B305" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A306" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B306" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A307" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="B307" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A308" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="B308" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A309" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="B309" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A310" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="B310" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A311" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="B311" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A312" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="B312" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A313" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B313" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A314" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="B314" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A315" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="B315" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A316" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="B316" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A317" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="B317" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A318" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="B318" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A319" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="B319" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A320" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="B320" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A321" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="B321" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A322" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="B322" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A323" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B323" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A324" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="B324" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A325" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="B325" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A326" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="B326" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A327" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="B327" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A328" s="6" t="s">
+        <v>334</v>
+      </c>
+      <c r="B328" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A329" s="6" t="s">
+        <v>335</v>
+      </c>
+      <c r="B329" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A330" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="B330" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A331" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="B331" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A332" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="B332" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A333" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B333" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A334" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="B334" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A335" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="B335" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A336" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="B336" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A337" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="B337" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A338" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="B338" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A339" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="B339" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A340" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="B340" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A341" s="6" t="s">
+        <v>347</v>
+      </c>
+      <c r="B341" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A342" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="B342" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A343" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="B343" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A344" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="B344" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A345" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="B345" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A346" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="B346" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A347" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="B347" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A348" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="B348" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A349" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="B349" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A350" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="B350" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A351" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="B351" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A352" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="B352" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A353" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="B353" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A354" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="B354" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A355" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="B355" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A356" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="B356" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A357" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="B357" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A358" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="B358" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A359" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="B359" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A360" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="B360" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A361" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="B361" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A362" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="B362" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A363" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="B363" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A364" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="B364" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A365" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="B365" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A366" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="B366" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A367" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="B367" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A368" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="B368" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A369" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="B369" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A370" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="B370" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A371" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="B371" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A372" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="B372" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A373" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="B373" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A374" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="B374" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A375" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="B375" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A376" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="B376" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A377" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="B377" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A378" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="B378" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A379" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="B379" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A380" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="B380" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A381" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="B381" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A382" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="B382" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A383" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="B383" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A384" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="B384" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A385" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="B385" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A386" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="B386" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A387" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="B387" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A388" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="B388" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A389" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="B389" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A390" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="B390" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A391" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="B391" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A392" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="B392" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A393" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="B393" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A394" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="B394" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A395" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="B395" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A396" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="B396" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A397" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="B397" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A398" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="B398" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A399" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="B399" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A400" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="B400" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A401" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="B401" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A402" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="B402" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A403" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="B403" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A404" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="B404" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A405" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="B405" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A406" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="B406" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A407" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="B407" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A408" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="B408" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A409" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B409" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A410" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="B410" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A411" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="B411" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A412" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="B412" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A413" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="B413" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A414" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="B414" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A415" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="B415" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A416" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="B416" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A417" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="B417" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A418" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="B418" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A419" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="B419" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A420" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="B420" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A421" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="B421" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A422" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="B422" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A423" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B423" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A424" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="B424" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A425" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="B425" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A426" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="B426" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A427" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="B427" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A428" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="B428" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A429" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="B429" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A430" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="B430" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A431" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="B431" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A432" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="B432" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="433" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A433" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="B433" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="434" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A434" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="B434" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="435" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A435" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="B435" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="436" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A436" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B436" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="437" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A437" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="B437" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="438" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A438" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="B438" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="439" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A439" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="B439" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="440" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A440" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="B440" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="441" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A441" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="B441" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="442" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A442" s="6" t="s">
+        <v>448</v>
+      </c>
+      <c r="B442" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="443" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A443" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B443" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="444" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A444" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="B444" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="445" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A445" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="B445" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="446" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A446" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="B446" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="447" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A447" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="B447" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="448" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A448" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="B448" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="449" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A449" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="B449" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="450" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A450" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="B450" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="451" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A451" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="B451" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="452" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A452" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="B452" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="453" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A453" s="6" t="s">
+        <v>459</v>
+      </c>
+      <c r="B453" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="454" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A454" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="B454" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="455" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A455" s="6" t="s">
+        <v>461</v>
+      </c>
+      <c r="B455" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="456" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A456" s="6" t="s">
+        <v>462</v>
+      </c>
+      <c r="B456" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="457" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A457" s="6" t="s">
+        <v>463</v>
+      </c>
+      <c r="B457" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="458" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A458" s="6" t="s">
+        <v>464</v>
+      </c>
+      <c r="B458" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="459" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A459" s="6" t="s">
+        <v>465</v>
+      </c>
+      <c r="B459" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="460" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A460" s="6" t="s">
+        <v>466</v>
+      </c>
+      <c r="B460" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="461" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A461" s="6" t="s">
+        <v>467</v>
+      </c>
+      <c r="B461" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="462" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A462" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="B462" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="463" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A463" s="6" t="s">
+        <v>469</v>
+      </c>
+      <c r="B463" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="464" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A464" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="B464" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="465" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A465" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="B465" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="466" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A466" s="6" t="s">
+        <v>472</v>
+      </c>
+      <c r="B466" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="467" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A467" s="6" t="s">
+        <v>473</v>
+      </c>
+      <c r="B467" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="468" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A468" s="6" t="s">
+        <v>474</v>
+      </c>
+      <c r="B468" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="469" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A469" s="6" t="s">
+        <v>475</v>
+      </c>
+      <c r="B469" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="470" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A470" s="6" t="s">
+        <v>476</v>
+      </c>
+      <c r="B470" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="471" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A471" s="6" t="s">
+        <v>477</v>
+      </c>
+      <c r="B471" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="472" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A472" s="6" t="s">
+        <v>478</v>
+      </c>
+      <c r="B472" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="473" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A473" s="6" t="s">
+        <v>479</v>
+      </c>
+      <c r="B473" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="474" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A474" s="6" t="s">
+        <v>480</v>
+      </c>
+      <c r="B474" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="475" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A475" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="B475" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="476" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A476" s="6" t="s">
+        <v>482</v>
+      </c>
+      <c r="B476" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="477" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A477" s="6" t="s">
+        <v>483</v>
+      </c>
+      <c r="B477" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="478" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A478" s="6" t="s">
+        <v>484</v>
+      </c>
+      <c r="B478" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="479" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A479" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="B479" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="480" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A480" s="6" t="s">
+        <v>486</v>
+      </c>
+      <c r="B480" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="481" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A481" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="B481" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="482" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A482" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="B482" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="483" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A483" s="6" t="s">
+        <v>489</v>
+      </c>
+      <c r="B483" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="484" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A484" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="B484" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="485" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A485" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="B485" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="486" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A486" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="B486" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="487" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A487" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="B487" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="488" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A488" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="B488" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="489" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A489" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="B489" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="490" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A490" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="B490" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="491" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A491" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="B491" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="492" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A492" s="6" t="s">
+        <v>498</v>
+      </c>
+      <c r="B492" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="493" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A493" s="6" t="s">
+        <v>499</v>
+      </c>
+      <c r="B493" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="494" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A494" s="6" t="s">
+        <v>500</v>
+      </c>
+      <c r="B494" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="495" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A495" s="6" t="s">
+        <v>501</v>
+      </c>
+      <c r="B495" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="496" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A496" s="6" t="s">
+        <v>502</v>
+      </c>
+      <c r="B496" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="497" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A497" s="6" t="s">
+        <v>503</v>
+      </c>
+      <c r="B497" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="498" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A498" s="6" t="s">
+        <v>504</v>
+      </c>
+      <c r="B498" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="499" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A499" s="6" t="s">
+        <v>505</v>
+      </c>
+      <c r="B499" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="500" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A500" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="B500" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="501" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A501" s="6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B501" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="502" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A502" s="6" t="s">
+        <v>508</v>
+      </c>
+      <c r="B502" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="503" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A503" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="B503" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="504" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A504" s="6" t="s">
+        <v>510</v>
+      </c>
+      <c r="B504" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="505" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A505" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="B505" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="506" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A506" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="B506" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="507" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A507" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="B507" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="508" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A508" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="B508" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="509" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A509" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="B509" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="510" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A510" s="6" t="s">
+        <v>516</v>
+      </c>
+      <c r="B510" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="511" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A511" s="6" t="s">
+        <v>517</v>
+      </c>
+      <c r="B511" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="512" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A512" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="B512" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="513" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A513" s="6" t="s">
+        <v>519</v>
+      </c>
+      <c r="B513" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="514" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A514" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="B514" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="515" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A515" s="6" t="s">
+        <v>521</v>
+      </c>
+      <c r="B515" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="516" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A516" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="B516" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="517" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A517" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="B517" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="518" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A518" s="6" t="s">
+        <v>524</v>
+      </c>
+      <c r="B518" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="519" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A519" s="6" t="s">
+        <v>525</v>
+      </c>
+      <c r="B519" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="520" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A520" s="6" t="s">
+        <v>526</v>
+      </c>
+      <c r="B520" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="521" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A521" s="6" t="s">
+        <v>527</v>
+      </c>
+      <c r="B521" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="522" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A522" s="6" t="s">
+        <v>528</v>
+      </c>
+      <c r="B522" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="523" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A523" s="6" t="s">
+        <v>529</v>
+      </c>
+      <c r="B523" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="524" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A524" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="B524" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="525" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A525" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="B525" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="526" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A526" s="6" t="s">
+        <v>532</v>
+      </c>
+      <c r="B526" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="527" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A527" s="6" t="s">
+        <v>533</v>
+      </c>
+      <c r="B527" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="528" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A528" s="6" t="s">
+        <v>534</v>
+      </c>
+      <c r="B528" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="529" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A529" s="6" t="s">
+        <v>535</v>
+      </c>
+      <c r="B529" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="530" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A530" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="B530" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="531" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A531" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="B531" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="532" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A532" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="B532" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="533" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A533" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="B533" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="534" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A534" s="6" t="s">
+        <v>540</v>
+      </c>
+      <c r="B534" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="535" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A535" s="6" t="s">
+        <v>541</v>
+      </c>
+      <c r="B535" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="536" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A536" s="6" t="s">
+        <v>542</v>
+      </c>
+      <c r="B536" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="537" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A537" s="6" t="s">
+        <v>543</v>
+      </c>
+      <c r="B537" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="538" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A538" s="6" t="s">
+        <v>544</v>
+      </c>
+      <c r="B538" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="539" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A539" s="6" t="s">
+        <v>545</v>
+      </c>
+      <c r="B539" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="540" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A540" s="6" t="s">
+        <v>546</v>
+      </c>
+      <c r="B540" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="541" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A541" s="6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B541" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="542" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A542" s="6" t="s">
+        <v>548</v>
+      </c>
+      <c r="B542" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="543" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A543" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="B543" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="544" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A544" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="B544" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="545" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A545" s="6" t="s">
+        <v>551</v>
+      </c>
+      <c r="B545" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="546" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A546" s="6" t="s">
+        <v>552</v>
+      </c>
+      <c r="B546" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A547" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="B547" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="548" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A548" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="B548" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="549" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A549" s="6" t="s">
+        <v>555</v>
+      </c>
+      <c r="B549" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="550" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A550" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="B550" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="551" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A551" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="B551" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="552" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A552" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="B552" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="553" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A553" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="B553" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="554" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A554" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="B554" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="555" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A555" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="B555" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="556" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A556" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="B556" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="557" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A557" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="B557" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="558" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A558" s="6" t="s">
+        <v>564</v>
+      </c>
+      <c r="B558" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="559" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A559" s="6" t="s">
+        <v>565</v>
+      </c>
+      <c r="B559" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="560" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A560" s="6" t="s">
+        <v>566</v>
+      </c>
+      <c r="B560" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="561" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A561" s="6" t="s">
+        <v>567</v>
+      </c>
+      <c r="B561" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="562" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A562" s="6" t="s">
+        <v>568</v>
+      </c>
+      <c r="B562" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="563" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A563" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="B563" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="564" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A564" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="B564" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="565" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A565" s="6" t="s">
+        <v>571</v>
+      </c>
+      <c r="B565" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="566" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A566" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="B566" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="567" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A567" s="6" t="s">
+        <v>573</v>
+      </c>
+      <c r="B567" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="568" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A568" s="6" t="s">
+        <v>574</v>
+      </c>
+      <c r="B568" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="569" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A569" s="6" t="s">
+        <v>575</v>
+      </c>
+      <c r="B569" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="570" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A570" s="6" t="s">
+        <v>576</v>
+      </c>
+      <c r="B570" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="571" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A571" s="6" t="s">
+        <v>577</v>
+      </c>
+      <c r="B571" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="572" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A572" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="B572" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="573" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A573" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="B573" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="574" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A574" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="B574" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="575" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A575" s="6" t="s">
+        <v>581</v>
+      </c>
+      <c r="B575" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="576" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A576" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="B576" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="577" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A577" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="B577" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="578" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A578" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="B578" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="579" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A579" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="B579" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="580" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A580" s="6" t="s">
+        <v>586</v>
+      </c>
+      <c r="B580" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="581" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A581" s="6" t="s">
+        <v>587</v>
+      </c>
+      <c r="B581" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="582" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A582" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="B582" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="583" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A583" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="B583" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="584" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A584" s="6" t="s">
+        <v>590</v>
+      </c>
+      <c r="B584" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="585" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A585" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="B585" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="586" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A586" s="6" t="s">
+        <v>592</v>
+      </c>
+      <c r="B586" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="587" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A587" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="B587" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="588" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A588" s="6" t="s">
+        <v>594</v>
+      </c>
+      <c r="B588" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="589" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A589" s="6" t="s">
+        <v>595</v>
+      </c>
+      <c r="B589" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="590" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A590" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="B590" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="591" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A591" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="B591" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="592" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A592" s="6" t="s">
+        <v>598</v>
+      </c>
+      <c r="B592" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="593" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A593" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="B593" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="594" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A594" s="6" t="s">
+        <v>600</v>
+      </c>
+      <c r="B594" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="595" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A595" s="6" t="s">
+        <v>601</v>
+      </c>
+      <c r="B595" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="596" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A596" s="6" t="s">
+        <v>602</v>
+      </c>
+      <c r="B596" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="597" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A597" s="6" t="s">
+        <v>603</v>
+      </c>
+      <c r="B597" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="598" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A598" s="6" t="s">
+        <v>604</v>
+      </c>
+      <c r="B598" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="599" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A599" s="6" t="s">
+        <v>605</v>
+      </c>
+      <c r="B599" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="600" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A600" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="B600" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="601" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A601" s="6" t="s">
+        <v>607</v>
+      </c>
+      <c r="B601" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="602" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A602" s="6" t="s">
+        <v>608</v>
+      </c>
+      <c r="B602" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="603" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A603" s="6" t="s">
+        <v>609</v>
+      </c>
+      <c r="B603" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="604" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A604" s="6" t="s">
+        <v>610</v>
+      </c>
+      <c r="B604" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="605" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A605" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="B605" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="606" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A606" s="6" t="s">
+        <v>612</v>
+      </c>
+      <c r="B606" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="607" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A607" s="6" t="s">
+        <v>613</v>
+      </c>
+      <c r="B607" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="608" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A608" s="6" t="s">
+        <v>614</v>
+      </c>
+      <c r="B608" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="609" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A609" s="6" t="s">
+        <v>615</v>
+      </c>
+      <c r="B609" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="610" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A610" s="6" t="s">
+        <v>616</v>
+      </c>
+      <c r="B610" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="611" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A611" s="6" t="s">
+        <v>617</v>
+      </c>
+      <c r="B611" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="612" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A612" s="6" t="s">
+        <v>618</v>
+      </c>
+      <c r="B612" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="613" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A613" s="6" t="s">
+        <v>619</v>
+      </c>
+      <c r="B613" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="614" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A614" s="6" t="s">
+        <v>620</v>
+      </c>
+      <c r="B614" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="615" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A615" s="6" t="s">
+        <v>621</v>
+      </c>
+      <c r="B615" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="616" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A616" s="6" t="s">
+        <v>622</v>
+      </c>
+      <c r="B616" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="617" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A617" s="6" t="s">
+        <v>623</v>
+      </c>
+      <c r="B617" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="618" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A618" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="B618" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="619" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A619" s="6" t="s">
+        <v>625</v>
+      </c>
+      <c r="B619" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="620" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A620" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="B620" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="621" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A621" s="6" t="s">
+        <v>627</v>
+      </c>
+      <c r="B621" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="622" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A622" s="6" t="s">
+        <v>628</v>
+      </c>
+      <c r="B622" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="623" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A623" s="6" t="s">
+        <v>629</v>
+      </c>
+      <c r="B623" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="624" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A624" s="6" t="s">
+        <v>630</v>
+      </c>
+      <c r="B624" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="625" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A625" s="6" t="s">
+        <v>631</v>
+      </c>
+      <c r="B625" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="626" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A626" s="6" t="s">
+        <v>632</v>
+      </c>
+      <c r="B626" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="627" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A627" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="B627" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="628" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A628" s="6" t="s">
+        <v>634</v>
+      </c>
+      <c r="B628" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="629" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A629" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="B629" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="630" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A630" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="B630" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="631" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A631" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="B631" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="632" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A632" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="B632" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="633" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A633" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="B633" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="634" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A634" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="B634" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="635" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A635" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="B635" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="636" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A636" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="B636" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="637" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A637" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="B637" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="638" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A638" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="B638" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="639" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A639" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="B639" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="640" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A640" s="6" t="s">
+        <v>646</v>
+      </c>
+      <c r="B640" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="641" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A641" s="6" t="s">
+        <v>647</v>
+      </c>
+      <c r="B641" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="642" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A642" s="6" t="s">
+        <v>648</v>
+      </c>
+      <c r="B642" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="643" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A643" s="6" t="s">
+        <v>649</v>
+      </c>
+      <c r="B643" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="644" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A644" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="B644" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="645" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A645" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="B645" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="646" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A646" s="6" t="s">
+        <v>652</v>
+      </c>
+      <c r="B646" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A647" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="B647" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="648" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A648" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="B648" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="649" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A649" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="B649" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="650" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A650" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="B650" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="651" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A651" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="B651" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="652" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A652" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="B652" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="653" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A653" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="B653" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="654" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A654" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="B654" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="655" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A655" s="6" t="s">
+        <v>661</v>
+      </c>
+      <c r="B655" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="656" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A656" s="6" t="s">
+        <v>662</v>
+      </c>
+      <c r="B656" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="657" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A657" s="6" t="s">
+        <v>663</v>
+      </c>
+      <c r="B657" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="658" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A658" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="B658" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="659" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A659" s="6" t="s">
+        <v>665</v>
+      </c>
+      <c r="B659" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="660" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A660" s="6" t="s">
+        <v>666</v>
+      </c>
+      <c r="B660" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="661" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A661" s="6" t="s">
+        <v>667</v>
+      </c>
+      <c r="B661" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="662" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A662" s="6" t="s">
+        <v>668</v>
+      </c>
+      <c r="B662" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="663" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A663" s="6" t="s">
+        <v>669</v>
+      </c>
+      <c r="B663" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="664" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A664" s="6" t="s">
+        <v>670</v>
+      </c>
+      <c r="B664" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="665" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A665" s="6" t="s">
+        <v>671</v>
+      </c>
+      <c r="B665" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="666" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A666" s="6" t="s">
+        <v>672</v>
+      </c>
+      <c r="B666" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="667" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A667" s="6" t="s">
+        <v>673</v>
+      </c>
+      <c r="B667" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="668" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A668" s="6" t="s">
+        <v>674</v>
+      </c>
+      <c r="B668" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="669" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A669" s="6" t="s">
+        <v>675</v>
+      </c>
+      <c r="B669" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="670" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A670" s="6" t="s">
+        <v>676</v>
+      </c>
+      <c r="B670" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="671" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A671" s="6" t="s">
+        <v>677</v>
+      </c>
+      <c r="B671" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="672" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A672" s="6" t="s">
+        <v>678</v>
+      </c>
+      <c r="B672" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="673" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A673" s="6" t="s">
+        <v>679</v>
+      </c>
+      <c r="B673" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="674" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A674" s="6" t="s">
+        <v>680</v>
+      </c>
+      <c r="B674" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="675" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A675" s="6" t="s">
+        <v>681</v>
+      </c>
+      <c r="B675" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="676" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A676" s="6" t="s">
+        <v>682</v>
+      </c>
+      <c r="B676" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="677" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A677" s="6" t="s">
+        <v>683</v>
+      </c>
+      <c r="B677" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="678" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A678" s="6" t="s">
+        <v>684</v>
+      </c>
+      <c r="B678" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="679" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A679" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="B679" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="680" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A680" s="6" t="s">
+        <v>686</v>
+      </c>
+      <c r="B680" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="681" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A681" s="6" t="s">
+        <v>687</v>
+      </c>
+      <c r="B681" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="682" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A682" s="6" t="s">
+        <v>688</v>
+      </c>
+      <c r="B682" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="683" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A683" s="6" t="s">
+        <v>689</v>
+      </c>
+      <c r="B683" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="684" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A684" s="6" t="s">
+        <v>690</v>
+      </c>
+      <c r="B684" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="685" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A685" s="6" t="s">
+        <v>691</v>
+      </c>
+      <c r="B685" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="686" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A686" s="6" t="s">
+        <v>692</v>
+      </c>
+      <c r="B686" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="687" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A687" s="6" t="s">
+        <v>693</v>
+      </c>
+      <c r="B687" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="688" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A688" s="6" t="s">
+        <v>694</v>
+      </c>
+      <c r="B688" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="689" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A689" s="6" t="s">
+        <v>695</v>
+      </c>
+      <c r="B689" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="690" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A690" s="6" t="s">
+        <v>696</v>
+      </c>
+      <c r="B690" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="691" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A691" s="6" t="s">
+        <v>697</v>
+      </c>
+      <c r="B691" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="692" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A692" s="6" t="s">
+        <v>698</v>
+      </c>
+      <c r="B692" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="693" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A693" s="6" t="s">
+        <v>699</v>
+      </c>
+      <c r="B693" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="694" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A694" s="6" t="s">
+        <v>700</v>
+      </c>
+      <c r="B694" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="695" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A695" s="6" t="s">
+        <v>701</v>
+      </c>
+      <c r="B695" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="696" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A696" s="6" t="s">
+        <v>702</v>
+      </c>
+      <c r="B696" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="697" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A697" s="6" t="s">
+        <v>703</v>
+      </c>
+      <c r="B697" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="698" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A698" s="6" t="s">
+        <v>704</v>
+      </c>
+      <c r="B698" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="699" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A699" s="6" t="s">
+        <v>705</v>
+      </c>
+      <c r="B699" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="700" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A700" s="6" t="s">
+        <v>706</v>
+      </c>
+      <c r="B700" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="701" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A701" s="6" t="s">
+        <v>707</v>
+      </c>
+      <c r="B701" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="702" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A702" s="6" t="s">
+        <v>708</v>
+      </c>
+      <c r="B702" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="703" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A703" s="6" t="s">
+        <v>709</v>
+      </c>
+      <c r="B703" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="704" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A704" s="6" t="s">
+        <v>710</v>
+      </c>
+      <c r="B704" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="705" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A705" s="6" t="s">
+        <v>711</v>
+      </c>
+      <c r="B705" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="706" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A706" s="6" t="s">
+        <v>712</v>
+      </c>
+      <c r="B706" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="707" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A707" s="6" t="s">
+        <v>713</v>
+      </c>
+      <c r="B707" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="708" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A708" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="B708" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="709" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A709" s="6" t="s">
+        <v>715</v>
+      </c>
+      <c r="B709" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="710" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A710" s="6" t="s">
+        <v>716</v>
+      </c>
+      <c r="B710" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="711" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A711" s="6" t="s">
+        <v>717</v>
+      </c>
+      <c r="B711" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="712" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A712" s="6" t="s">
+        <v>718</v>
+      </c>
+      <c r="B712" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="713" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A713" s="6" t="s">
+        <v>719</v>
+      </c>
+      <c r="B713" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="714" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A714" s="6" t="s">
+        <v>720</v>
+      </c>
+      <c r="B714" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="715" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A715" s="6" t="s">
+        <v>721</v>
+      </c>
+      <c r="B715" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="716" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A716" s="6" t="s">
+        <v>722</v>
+      </c>
+      <c r="B716" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="717" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A717" s="6" t="s">
+        <v>723</v>
+      </c>
+      <c r="B717" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="718" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A718" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="B718" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="719" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A719" s="6" t="s">
+        <v>725</v>
+      </c>
+      <c r="B719" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="720" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A720" s="6" t="s">
+        <v>726</v>
+      </c>
+      <c r="B720" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="721" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A721" s="6" t="s">
+        <v>727</v>
+      </c>
+      <c r="B721" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="722" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A722" s="6" t="s">
+        <v>728</v>
+      </c>
+      <c r="B722" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="723" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A723" s="6" t="s">
+        <v>729</v>
+      </c>
+      <c r="B723" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="724" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A724" s="6" t="s">
+        <v>730</v>
+      </c>
+      <c r="B724" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="725" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A725" s="6" t="s">
+        <v>731</v>
+      </c>
+      <c r="B725" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="726" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A726" s="6" t="s">
+        <v>732</v>
+      </c>
+      <c r="B726" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="727" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A727" s="6" t="s">
+        <v>733</v>
+      </c>
+      <c r="B727" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="728" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A728" s="6" t="s">
+        <v>734</v>
+      </c>
+      <c r="B728" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="729" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A729" s="6" t="s">
+        <v>735</v>
+      </c>
+      <c r="B729" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="730" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A730" s="6" t="s">
+        <v>736</v>
+      </c>
+      <c r="B730" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="731" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A731" s="6" t="s">
+        <v>737</v>
+      </c>
+      <c r="B731" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="732" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A732" s="6" t="s">
+        <v>738</v>
+      </c>
+      <c r="B732" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="733" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A733" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="B733" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="734" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A734" s="6" t="s">
+        <v>740</v>
+      </c>
+      <c r="B734" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="735" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A735" s="6" t="s">
+        <v>741</v>
+      </c>
+      <c r="B735" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="736" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A736" s="6" t="s">
+        <v>742</v>
+      </c>
+      <c r="B736" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="737" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A737" s="6" t="s">
+        <v>743</v>
+      </c>
+      <c r="B737" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="738" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A738" s="6" t="s">
+        <v>744</v>
+      </c>
+      <c r="B738" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="739" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A739" s="6" t="s">
+        <v>745</v>
+      </c>
+      <c r="B739" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="740" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A740" s="6" t="s">
+        <v>746</v>
+      </c>
+      <c r="B740" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="741" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A741" s="6" t="s">
+        <v>747</v>
+      </c>
+      <c r="B741" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="742" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A742" s="6" t="s">
+        <v>748</v>
+      </c>
+      <c r="B742" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="743" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A743" s="6" t="s">
+        <v>749</v>
+      </c>
+      <c r="B743" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="744" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A744" s="6" t="s">
+        <v>750</v>
+      </c>
+      <c r="B744" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="745" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A745" s="6" t="s">
+        <v>751</v>
+      </c>
+      <c r="B745" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="746" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A746" s="6" t="s">
+        <v>752</v>
+      </c>
+      <c r="B746" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="747" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A747" s="6" t="s">
+        <v>753</v>
+      </c>
+      <c r="B747" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="748" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A748" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="B748" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="749" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A749" s="6" t="s">
+        <v>755</v>
+      </c>
+      <c r="B749" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A750" s="6" t="s">
+        <v>756</v>
+      </c>
+      <c r="B750" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="751" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A751" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="B751" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="752" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A752" s="6" t="s">
+        <v>758</v>
+      </c>
+      <c r="B752" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="753" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A753" s="6" t="s">
+        <v>759</v>
+      </c>
+      <c r="B753" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="754" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A754" s="6" t="s">
+        <v>760</v>
+      </c>
+      <c r="B754" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="755" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A755" s="6" t="s">
+        <v>761</v>
+      </c>
+      <c r="B755" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="756" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A756" s="6" t="s">
+        <v>762</v>
+      </c>
+      <c r="B756" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="757" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A757" s="6" t="s">
+        <v>763</v>
+      </c>
+      <c r="B757" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="758" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A758" s="6" t="s">
+        <v>764</v>
+      </c>
+      <c r="B758" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="759" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A759" s="6" t="s">
+        <v>765</v>
+      </c>
+      <c r="B759" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="760" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A760" s="6" t="s">
+        <v>766</v>
+      </c>
+      <c r="B760" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="761" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A761" s="6" t="s">
+        <v>767</v>
+      </c>
+      <c r="B761" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="762" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A762" s="6" t="s">
+        <v>768</v>
+      </c>
+      <c r="B762" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="763" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A763" s="6" t="s">
+        <v>769</v>
+      </c>
+      <c r="B763" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="764" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A764" s="6" t="s">
+        <v>770</v>
+      </c>
+      <c r="B764" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="765" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A765" s="6" t="s">
+        <v>771</v>
+      </c>
+      <c r="B765" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="766" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A766" s="6" t="s">
+        <v>772</v>
+      </c>
+      <c r="B766" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="767" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A767" s="6" t="s">
+        <v>773</v>
+      </c>
+      <c r="B767" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="768" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A768" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="B768" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="769" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A769" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="B769" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="770" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A770" s="6" t="s">
+        <v>776</v>
+      </c>
+      <c r="B770" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="771" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A771" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="B771" s="4">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B210" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <autoFilter ref="A1:B612" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <conditionalFormatting sqref="A1 C511:C525 A772:A1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C235:C264">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C318:C322">
+    <cfRule type="duplicateValues" dxfId="1" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A771">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$BM2="Гүйлгээ хийгдээгүй"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <ignoredErrors>
-    <ignoredError sqref="A141" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
@@ -2273,32 +9059,32 @@
   <sheetData>
     <row r="1" spans="1:1" ht="19" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
